--- a/output/20260630_fix_owner_new_import/fitbase_import_uslugi_clientov_20260630.xlsx
+++ b/output/20260630_fix_owner_new_import/fitbase_import_uslugi_clientov_20260630.xlsx
@@ -656,7 +656,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
     </row>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
     </row>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
     </row>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
     </row>
@@ -12147,7 +12147,7 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
     </row>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
@@ -12757,7 +12757,7 @@
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
     </row>
@@ -13291,7 +13291,7 @@
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
     </row>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
@@ -14365,7 +14365,7 @@
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
@@ -14426,7 +14426,7 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
     </row>
@@ -14667,7 +14667,7 @@
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
     </row>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
@@ -15717,7 +15717,7 @@
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
     </row>
@@ -18247,7 +18247,7 @@
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
     </row>
@@ -18610,7 +18610,7 @@
       </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
     </row>
@@ -19028,7 +19028,7 @@
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
@@ -19086,7 +19086,7 @@
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
@@ -19147,7 +19147,7 @@
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
     </row>
@@ -19327,7 +19327,7 @@
       </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
     </row>
@@ -19986,7 +19986,7 @@
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
     </row>
@@ -20941,7 +20941,7 @@
       </c>
       <c r="P343" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
     </row>
@@ -21405,7 +21405,7 @@
       </c>
       <c r="P351" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
     </row>
@@ -23243,7 +23243,7 @@
       </c>
       <c r="P380" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
@@ -23991,7 +23991,7 @@
       </c>
       <c r="P392" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
@@ -27059,7 +27059,7 @@
       </c>
       <c r="P440" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
     </row>
@@ -28595,7 +28595,7 @@
       </c>
       <c r="P464" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>

--- a/output/20260630_fix_owner_new_import/fitbase_import_uslugi_clientov_20260630.xlsx
+++ b/output/20260630_fix_owner_new_import/fitbase_import_uslugi_clientov_20260630.xlsx
@@ -6,7 +6,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист1'!$A$1:$P$530</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист1'!$A$1:$P$524</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P530"/>
+  <dimension ref="A1:P524"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12" customWidth="1" style="21" min="1" max="1"/>
@@ -22802,22 +22802,22 @@
     <row r="374" ht="15.75" customHeight="1" s="21">
       <c r="A374" t="inlineStr">
         <is>
-          <t>00000030211-1</t>
+          <t>00000027597-1</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>000071728</t>
+          <t>000070219</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>+7 (911) 4094501</t>
+          <t>+7 (911) 6693126</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Зеленская София Викторовна</t>
+          <t>Баботина Александра Александровна</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -22826,16 +22826,16 @@
         </is>
       </c>
       <c r="F374" s="22" t="n">
-        <v>46166</v>
+        <v>46152</v>
       </c>
       <c r="G374" s="22" t="n">
-        <v>46166</v>
+        <v>46152</v>
       </c>
       <c r="H374" s="22" t="n">
-        <v>46166</v>
+        <v>46152</v>
       </c>
       <c r="I374" s="22" t="n">
-        <v>46166</v>
+        <v>46152</v>
       </c>
       <c r="J374" t="n">
         <v>1</v>
@@ -22859,7 +22859,7 @@
       </c>
       <c r="P374" t="inlineStr">
         <is>
-          <t>Фёдорова Надежда Сергеевна</t>
+          <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
     </row>
@@ -26746,22 +26746,22 @@
     <row r="436" ht="15.75" customHeight="1" s="21">
       <c r="A436" t="inlineStr">
         <is>
-          <t>00000001778-1</t>
+          <t>00000001968-1</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>000020906</t>
+          <t>000009610</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7 (921) 2242819</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Розничный клиент</t>
+          <t>Лаврукова Любовь Александровна</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -26773,7 +26773,7 @@
         <v>43844</v>
       </c>
       <c r="G436" s="22" t="n">
-        <v>43844</v>
+        <v>43845</v>
       </c>
       <c r="H436" s="22" t="n">
         <v>43844</v>
@@ -26803,29 +26803,29 @@
       </c>
       <c r="P436" t="inlineStr">
         <is>
-          <t>Фёдорова Милана Андреевна</t>
+          <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
     </row>
     <row r="437" ht="15.75" customHeight="1" s="21">
       <c r="A437" t="inlineStr">
         <is>
-          <t>00000035778-1</t>
+          <t>00000001778-1</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>000027722</t>
+          <t>000020906</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>+7 (911) 4242113</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Гарлоев Денис Владимирович</t>
+          <t>Розничный клиент</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -26834,16 +26834,16 @@
         </is>
       </c>
       <c r="F437" s="22" t="n">
-        <v>44514</v>
+        <v>43844</v>
       </c>
       <c r="G437" s="22" t="n">
-        <v>44514</v>
+        <v>43844</v>
       </c>
       <c r="H437" s="22" t="n">
-        <v>44514</v>
+        <v>43844</v>
       </c>
       <c r="I437" s="22" t="n">
-        <v>44514</v>
+        <v>43844</v>
       </c>
       <c r="J437" t="n">
         <v>1</v>
@@ -26867,29 +26867,29 @@
       </c>
       <c r="P437" t="inlineStr">
         <is>
-          <t>Мартынова Дарья Дмитриевна</t>
+          <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
     </row>
     <row r="438" ht="15.75" customHeight="1" s="21">
       <c r="A438" t="inlineStr">
         <is>
-          <t>00000047300-2</t>
+          <t>00000035778-1</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>000050759</t>
+          <t>000027722</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>+7 (921) 6233884</t>
+          <t>+7 (911) 4242113</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Носова Юлия Андреевна</t>
+          <t>Гарлоев Денис Владимирович</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -26898,16 +26898,16 @@
         </is>
       </c>
       <c r="F438" s="22" t="n">
-        <v>44805</v>
+        <v>44514</v>
       </c>
       <c r="G438" s="22" t="n">
-        <v>44805</v>
+        <v>44514</v>
       </c>
       <c r="H438" s="22" t="n">
-        <v>44805</v>
+        <v>44514</v>
       </c>
       <c r="I438" s="22" t="n">
-        <v>44805</v>
+        <v>44514</v>
       </c>
       <c r="J438" t="n">
         <v>1</v>
@@ -26931,29 +26931,29 @@
       </c>
       <c r="P438" t="inlineStr">
         <is>
-          <t>Васильева Яна Денисовна</t>
+          <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
     </row>
     <row r="439" ht="15.75" customHeight="1" s="21">
       <c r="A439" t="inlineStr">
         <is>
-          <t>00000059839-1</t>
+          <t>00000047300-2</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>000065381</t>
+          <t>000050759</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>+7 (921) 5225218</t>
+          <t>+7 (921) 6233884</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Лобанов Александр Сергеевич</t>
+          <t>Носова Юлия Андреевна</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -26962,16 +26962,16 @@
         </is>
       </c>
       <c r="F439" s="22" t="n">
-        <v>45607</v>
+        <v>44805</v>
       </c>
       <c r="G439" s="22" t="n">
-        <v>45607</v>
+        <v>44805</v>
       </c>
       <c r="H439" s="22" t="n">
-        <v>45607</v>
+        <v>44805</v>
       </c>
       <c r="I439" s="22" t="n">
-        <v>45607</v>
+        <v>44805</v>
       </c>
       <c r="J439" t="n">
         <v>1</v>
@@ -26995,29 +26995,29 @@
       </c>
       <c r="P439" t="inlineStr">
         <is>
-          <t>Седунова Анна Сергеевна</t>
+          <t>Васильева Яна Денисовна</t>
         </is>
       </c>
     </row>
     <row r="440" ht="15.75" customHeight="1" s="21">
       <c r="A440" t="inlineStr">
         <is>
-          <t>00000021988-1</t>
+          <t>00000026297-1</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>000046331</t>
+          <t>000010034</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>+7 (911) 4381279</t>
+          <t>+7 (953) 5299933</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Челмаева Анна Ивановна</t>
+          <t>Либман Екатерина Семеновна</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -27026,16 +27026,16 @@
         </is>
       </c>
       <c r="F440" s="22" t="n">
-        <v>45035</v>
+        <v>44414</v>
       </c>
       <c r="G440" s="22" t="n">
-        <v>45035</v>
+        <v>44414</v>
       </c>
       <c r="H440" s="22" t="n">
-        <v>45035</v>
+        <v>44414</v>
       </c>
       <c r="I440" s="22" t="n">
-        <v>45035</v>
+        <v>44414</v>
       </c>
       <c r="J440" t="n">
         <v>1</v>
@@ -27059,29 +27059,29 @@
       </c>
       <c r="P440" t="inlineStr">
         <is>
-          <t>Соколова Анастасия Александровна</t>
+          <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
     </row>
     <row r="441" ht="15.75" customHeight="1" s="21">
       <c r="A441" t="inlineStr">
         <is>
-          <t>00000038468-1</t>
+          <t>00000007246-1</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>000055653</t>
+          <t>000012624</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>+7 (909) 5721232</t>
+          <t>+7 (911) 4033133</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Орлов Петр Олегович</t>
+          <t>Никулина Екатерина Андреевна</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -27090,16 +27090,16 @@
         </is>
       </c>
       <c r="F441" s="22" t="n">
-        <v>45127</v>
+        <v>44249</v>
       </c>
       <c r="G441" s="22" t="n">
-        <v>45127</v>
+        <v>44249</v>
       </c>
       <c r="H441" s="22" t="n">
-        <v>45127</v>
+        <v>44249</v>
       </c>
       <c r="I441" s="22" t="n">
-        <v>45127</v>
+        <v>44249</v>
       </c>
       <c r="J441" t="n">
         <v>1</v>
@@ -27123,29 +27123,29 @@
       </c>
       <c r="P441" t="inlineStr">
         <is>
-          <t>Васьковская Виктория Петровна</t>
+          <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
     </row>
     <row r="442" ht="15.75" customHeight="1" s="21">
       <c r="A442" t="inlineStr">
         <is>
-          <t>00000017591-1</t>
+          <t>00000021988-1</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>000057475</t>
+          <t>000046331</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>+7 (911) 4264251</t>
+          <t>+7 (911) 4381279</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Магурина Наталья Александровна</t>
+          <t>Челмаева Анна Ивановна</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -27154,16 +27154,16 @@
         </is>
       </c>
       <c r="F442" s="22" t="n">
-        <v>45015</v>
+        <v>45035</v>
       </c>
       <c r="G442" s="22" t="n">
-        <v>45015</v>
+        <v>45035</v>
       </c>
       <c r="H442" s="22" t="n">
-        <v>45015</v>
+        <v>45035</v>
       </c>
       <c r="I442" s="22" t="n">
-        <v>45015</v>
+        <v>45035</v>
       </c>
       <c r="J442" t="n">
         <v>1</v>
@@ -27187,29 +27187,29 @@
       </c>
       <c r="P442" t="inlineStr">
         <is>
-          <t>Пилия Анастасия Артуровна</t>
+          <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
     </row>
     <row r="443" ht="15.75" customHeight="1" s="21">
       <c r="A443" t="inlineStr">
         <is>
-          <t>00000017592-1</t>
+          <t>00000047300-1</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>000057475</t>
+          <t>000050759</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>+7 (911) 4264251</t>
+          <t>+7 (921) 6233884</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Магурина Наталья Александровна</t>
+          <t>Носова Юлия Андреевна</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -27218,16 +27218,16 @@
         </is>
       </c>
       <c r="F443" s="22" t="n">
-        <v>45015</v>
+        <v>44805</v>
       </c>
       <c r="G443" s="22" t="n">
-        <v>45015</v>
+        <v>44805</v>
       </c>
       <c r="H443" s="22" t="n">
-        <v>45015</v>
+        <v>44805</v>
       </c>
       <c r="I443" s="22" t="n">
-        <v>45015</v>
+        <v>44805</v>
       </c>
       <c r="J443" t="n">
         <v>1</v>
@@ -27251,29 +27251,29 @@
       </c>
       <c r="P443" t="inlineStr">
         <is>
-          <t>Пилия Анастасия Артуровна</t>
+          <t>Васильева Яна Денисовна</t>
         </is>
       </c>
     </row>
     <row r="444" ht="15.75" customHeight="1" s="21">
       <c r="A444" t="inlineStr">
         <is>
-          <t>00000017593-1</t>
+          <t>00000038468-1</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>000057475</t>
+          <t>000055653</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>+7 (911) 4264251</t>
+          <t>+7 (909) 5721232</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Магурина Наталья Александровна</t>
+          <t>Орлов Петр Олегович</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -27282,16 +27282,16 @@
         </is>
       </c>
       <c r="F444" s="22" t="n">
-        <v>45015</v>
+        <v>45127</v>
       </c>
       <c r="G444" s="22" t="n">
-        <v>45015</v>
+        <v>45127</v>
       </c>
       <c r="H444" s="22" t="n">
-        <v>45015</v>
+        <v>45127</v>
       </c>
       <c r="I444" s="22" t="n">
-        <v>45015</v>
+        <v>45127</v>
       </c>
       <c r="J444" t="n">
         <v>1</v>
@@ -27315,7 +27315,7 @@
       </c>
       <c r="P444" t="inlineStr">
         <is>
-          <t>Пилия Анастасия Артуровна</t>
+          <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
     </row>
@@ -27706,22 +27706,22 @@
     <row r="451" ht="15.75" customHeight="1" s="21">
       <c r="A451" t="inlineStr">
         <is>
-          <t>00000070899-1</t>
+          <t>00000060580-2</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>000036625</t>
+          <t>000029717</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>+7 (921) 5207613</t>
+          <t>+7 (911) 4301995</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Матвеев Денис Николаевич</t>
+          <t>Амосов Алексей Анатольевич</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -27730,16 +27730,16 @@
         </is>
       </c>
       <c r="F451" s="22" t="n">
-        <v>45657</v>
+        <v>45609</v>
       </c>
       <c r="G451" s="22" t="n">
-        <v>45657</v>
+        <v>45609</v>
       </c>
       <c r="H451" s="22" t="n">
-        <v>45657</v>
+        <v>45609</v>
       </c>
       <c r="I451" s="22" t="n">
-        <v>45657</v>
+        <v>45609</v>
       </c>
       <c r="J451" t="n">
         <v>1</v>
@@ -27763,29 +27763,29 @@
       </c>
       <c r="P451" t="inlineStr">
         <is>
-          <t>Абраамян Татьяна Викторовна</t>
+          <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
     </row>
     <row r="452" ht="15.75" customHeight="1" s="21">
       <c r="A452" t="inlineStr">
         <is>
-          <t>00000073366-1</t>
+          <t>00000059763-1</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>000059253</t>
+          <t>000035931</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>+7 (911) 4110709</t>
+          <t>+7 (921) 4582966</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Лунёва Илона Юрьевна</t>
+          <t>Мельникова Дарья Леонидовна</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -27794,16 +27794,16 @@
         </is>
       </c>
       <c r="F452" s="22" t="n">
-        <v>46007</v>
+        <v>45606</v>
       </c>
       <c r="G452" s="22" t="n">
-        <v>46007</v>
+        <v>45606</v>
       </c>
       <c r="H452" s="22" t="n">
-        <v>46007</v>
+        <v>45606</v>
       </c>
       <c r="I452" s="22" t="n">
-        <v>46007</v>
+        <v>45606</v>
       </c>
       <c r="J452" t="n">
         <v>1</v>
@@ -27827,29 +27827,29 @@
       </c>
       <c r="P452" t="inlineStr">
         <is>
-          <t>Мартынова Дарья Дмитриевна</t>
+          <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
     </row>
     <row r="453" ht="15.75" customHeight="1" s="21">
       <c r="A453" t="inlineStr">
         <is>
-          <t>00000069766-1</t>
+          <t>00000070899-1</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>000059656</t>
+          <t>000036625</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>+7 (911) 6638283</t>
+          <t>+7 (921) 5207613</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Семёнова Наталия Борисовна</t>
+          <t>Матвеев Денис Николаевич</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -27858,16 +27858,16 @@
         </is>
       </c>
       <c r="F453" s="22" t="n">
-        <v>45653</v>
+        <v>45657</v>
       </c>
       <c r="G453" s="22" t="n">
-        <v>45653</v>
+        <v>45657</v>
       </c>
       <c r="H453" s="22" t="n">
-        <v>45653</v>
+        <v>45657</v>
       </c>
       <c r="I453" s="22" t="n">
-        <v>45653</v>
+        <v>45657</v>
       </c>
       <c r="J453" t="n">
         <v>1</v>
@@ -27891,29 +27891,29 @@
       </c>
       <c r="P453" t="inlineStr">
         <is>
-          <t>Яковлева Александра Владимировна</t>
+          <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
     </row>
     <row r="454" ht="15.75" customHeight="1" s="21">
       <c r="A454" t="inlineStr">
         <is>
-          <t>00000063445-1</t>
+          <t>00000073366-1</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>000066289</t>
+          <t>000059253</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>+7 (921) 6283656</t>
+          <t>+7 (911) 4110709</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Шестакова Екатерина Николаевна</t>
+          <t>Лунёва Илона Юрьевна</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -27922,16 +27922,16 @@
         </is>
       </c>
       <c r="F454" s="22" t="n">
-        <v>45623</v>
+        <v>46007</v>
       </c>
       <c r="G454" s="22" t="n">
-        <v>45623</v>
+        <v>46007</v>
       </c>
       <c r="H454" s="22" t="n">
-        <v>45623</v>
+        <v>46007</v>
       </c>
       <c r="I454" s="22" t="n">
-        <v>45623</v>
+        <v>46007</v>
       </c>
       <c r="J454" t="n">
         <v>1</v>
@@ -27955,7 +27955,7 @@
       </c>
       <c r="P454" t="inlineStr">
         <is>
-          <t>Васильева Яна Денисовна</t>
+          <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
     </row>
@@ -28026,22 +28026,22 @@
     <row r="456" ht="15.75" customHeight="1" s="21">
       <c r="A456" t="inlineStr">
         <is>
-          <t>00000043728-1</t>
+          <t>00000018860-1</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>000030442</t>
+          <t>000004703</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>+7 (921) 2240767</t>
+          <t>+7 (911) 4124527</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Тимичева Юлия Андреевна</t>
+          <t>Копылова Виктория Владимировна</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -28050,16 +28050,16 @@
         </is>
       </c>
       <c r="F456" s="22" t="n">
-        <v>45526</v>
+        <v>45384</v>
       </c>
       <c r="G456" s="22" t="n">
-        <v>45526</v>
+        <v>45384</v>
       </c>
       <c r="H456" s="22" t="n">
-        <v>45526</v>
+        <v>45384</v>
       </c>
       <c r="I456" s="22" t="n">
-        <v>45526</v>
+        <v>45384</v>
       </c>
       <c r="J456" t="n">
         <v>1</v>
@@ -28083,29 +28083,29 @@
       </c>
       <c r="P456" t="inlineStr">
         <is>
-          <t>Пеуна Анастасия Ивановна</t>
+          <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
     <row r="457" ht="15.75" customHeight="1" s="21">
       <c r="A457" t="inlineStr">
         <is>
-          <t>00000055714-1</t>
+          <t>00000043727-1</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>000032981</t>
+          <t>000030442</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>+7 (911) 4153483</t>
+          <t>+7 (921) 2240767</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Петрова Анастасия Андреевна</t>
+          <t>Тимичева Юлия Андреевна</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -28114,16 +28114,16 @@
         </is>
       </c>
       <c r="F457" s="22" t="n">
-        <v>45588</v>
+        <v>45526</v>
       </c>
       <c r="G457" s="22" t="n">
-        <v>45588</v>
+        <v>45526</v>
       </c>
       <c r="H457" s="22" t="n">
-        <v>45588</v>
+        <v>45526</v>
       </c>
       <c r="I457" s="22" t="n">
-        <v>45588</v>
+        <v>45526</v>
       </c>
       <c r="J457" t="n">
         <v>1</v>
@@ -28147,29 +28147,29 @@
       </c>
       <c r="P457" t="inlineStr">
         <is>
-          <t>Васильева Яна Денисовна</t>
+          <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
     </row>
     <row r="458" ht="15.75" customHeight="1" s="21">
       <c r="A458" t="inlineStr">
         <is>
-          <t>00000035243-1</t>
+          <t>00000043728-1</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>000049651</t>
+          <t>000030442</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>+7 (921) 4536971</t>
+          <t>+7 (921) 2240767</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Паппинен Арина Арвиевна</t>
+          <t>Тимичева Юлия Андреевна</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -28178,16 +28178,16 @@
         </is>
       </c>
       <c r="F458" s="22" t="n">
-        <v>45813</v>
+        <v>45526</v>
       </c>
       <c r="G458" s="22" t="n">
-        <v>45813</v>
+        <v>45526</v>
       </c>
       <c r="H458" s="22" t="n">
-        <v>45813</v>
+        <v>45526</v>
       </c>
       <c r="I458" s="22" t="n">
-        <v>45813</v>
+        <v>45526</v>
       </c>
       <c r="J458" t="n">
         <v>1</v>
@@ -28211,29 +28211,29 @@
       </c>
       <c r="P458" t="inlineStr">
         <is>
-          <t>Лисовская Екатерина Александровна</t>
+          <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
     </row>
     <row r="459" ht="15.75" customHeight="1" s="21">
       <c r="A459" t="inlineStr">
         <is>
-          <t>00000035243-2</t>
+          <t>00000055714-1</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>000049651</t>
+          <t>000032981</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>+7 (921) 4536971</t>
+          <t>+7 (911) 4153483</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Паппинен Арина Арвиевна</t>
+          <t>Петрова Анастасия Андреевна</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -28242,16 +28242,16 @@
         </is>
       </c>
       <c r="F459" s="22" t="n">
-        <v>45813</v>
+        <v>45588</v>
       </c>
       <c r="G459" s="22" t="n">
-        <v>45813</v>
+        <v>45588</v>
       </c>
       <c r="H459" s="22" t="n">
-        <v>45813</v>
+        <v>45588</v>
       </c>
       <c r="I459" s="22" t="n">
-        <v>45813</v>
+        <v>45588</v>
       </c>
       <c r="J459" t="n">
         <v>1</v>
@@ -28275,7 +28275,7 @@
       </c>
       <c r="P459" t="inlineStr">
         <is>
-          <t>Лисовская Екатерина Александровна</t>
+          <t>Васильева Яна Денисовна</t>
         </is>
       </c>
     </row>
@@ -29242,22 +29242,22 @@
     <row r="475" ht="15.75" customHeight="1" s="21">
       <c r="A475" t="inlineStr">
         <is>
-          <t>00000030203-1</t>
+          <t>00000030004-1</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>000053562</t>
+          <t>000001517</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>+7 (953) 5320103</t>
+          <t>+7 (953) 5462794</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Ермакова Алена Николаевна</t>
+          <t>Беляев Антон Сергеевич</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -29266,16 +29266,16 @@
         </is>
       </c>
       <c r="F475" s="22" t="n">
-        <v>46166</v>
+        <v>46164</v>
       </c>
       <c r="G475" s="22" t="n">
-        <v>46166</v>
+        <v>46164</v>
       </c>
       <c r="H475" s="22" t="n">
-        <v>46166</v>
+        <v>46164</v>
       </c>
       <c r="I475" s="22" t="n">
-        <v>46166</v>
+        <v>46164</v>
       </c>
       <c r="J475" t="n">
         <v>1</v>
@@ -29299,29 +29299,29 @@
       </c>
       <c r="P475" t="inlineStr">
         <is>
-          <t>Васильева Яна Денисовна</t>
+          <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
     </row>
     <row r="476" ht="15.75" customHeight="1" s="21">
       <c r="A476" t="inlineStr">
         <is>
-          <t>00000030202-1</t>
+          <t>00000030203-1</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>000067575</t>
+          <t>000053562</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>+7 (953) 5495131</t>
+          <t>+7 (953) 5320103</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Варфоломеев Денис Юрьевич</t>
+          <t>Ермакова Алена Николаевна</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -29363,7 +29363,7 @@
       </c>
       <c r="P476" t="inlineStr">
         <is>
-          <t>Мартынова Дарья Дмитриевна</t>
+          <t>Васильева Яна Денисовна</t>
         </is>
       </c>
     </row>
@@ -29434,22 +29434,22 @@
     <row r="478" ht="15.75" customHeight="1" s="21">
       <c r="A478" t="inlineStr">
         <is>
-          <t>00000030221-1</t>
+          <t>00000029758-1</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>000073977</t>
+          <t>000070323</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>+7 (917) 5629522</t>
+          <t>+7 (911) 4062806</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Кутепов Дмитрий Сергеевич</t>
+          <t>Трифанова Маргарита Вадимовна</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -29458,16 +29458,16 @@
         </is>
       </c>
       <c r="F478" s="22" t="n">
-        <v>46166</v>
+        <v>46163</v>
       </c>
       <c r="G478" s="22" t="n">
-        <v>46166</v>
+        <v>46163</v>
       </c>
       <c r="H478" s="22" t="n">
-        <v>46166</v>
+        <v>46163</v>
       </c>
       <c r="I478" s="22" t="n">
-        <v>46166</v>
+        <v>46163</v>
       </c>
       <c r="J478" t="n">
         <v>1</v>
@@ -29498,22 +29498,22 @@
     <row r="479" ht="15.75" customHeight="1" s="21">
       <c r="A479" t="inlineStr">
         <is>
-          <t>00000030237-1</t>
+          <t>00000029505-1</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>000073979</t>
+          <t>000070828</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>+7 (904) 5144271</t>
+          <t>+7 (921) 7018816</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Суворов Михаил Андреевич</t>
+          <t>Лощинина Ксения Дмитриевна</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -29522,16 +29522,16 @@
         </is>
       </c>
       <c r="F479" s="22" t="n">
-        <v>46166</v>
+        <v>46162</v>
       </c>
       <c r="G479" s="22" t="n">
-        <v>46166</v>
+        <v>46162</v>
       </c>
       <c r="H479" s="22" t="n">
-        <v>46166</v>
+        <v>46162</v>
       </c>
       <c r="I479" s="22" t="n">
-        <v>46166</v>
+        <v>46162</v>
       </c>
       <c r="J479" t="n">
         <v>1</v>
@@ -29555,7 +29555,7 @@
       </c>
       <c r="P479" t="inlineStr">
         <is>
-          <t>Седунова Анна Сергеевна</t>
+          <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
     </row>
@@ -29946,22 +29946,22 @@
     <row r="486" ht="15.75" customHeight="1" s="21">
       <c r="A486" t="inlineStr">
         <is>
-          <t>00000064616-1</t>
+          <t>00000001774-1</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>000070967</t>
+          <t>000071963</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>+7 (921) 1752216</t>
+          <t>+7 (911) 4002488</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Дегтяренко Юлия Константиновна</t>
+          <t>Багреева Мария Викторовна</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -29970,16 +29970,16 @@
         </is>
       </c>
       <c r="F486" s="22" t="n">
-        <v>45968</v>
+        <v>46034</v>
       </c>
       <c r="G486" s="22" t="n">
-        <v>45968</v>
+        <v>46034</v>
       </c>
       <c r="H486" s="22" t="n">
-        <v>45968</v>
+        <v>46034</v>
       </c>
       <c r="I486" s="22" t="n">
-        <v>45968</v>
+        <v>46034</v>
       </c>
       <c r="J486" t="n">
         <v>1</v>
@@ -29998,52 +29998,52 @@
       </c>
       <c r="O486" t="inlineStr">
         <is>
-          <t>сбп</t>
+          <t>безналичные</t>
         </is>
       </c>
       <c r="P486" t="inlineStr">
         <is>
-          <t>Пеуна Анастасия Ивановна</t>
+          <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
     </row>
     <row r="487" ht="15.75" customHeight="1" s="21">
       <c r="A487" t="inlineStr">
         <is>
-          <t>00000001774-1</t>
+          <t>00000024034-1</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>000071963</t>
+          <t>000007367</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>+7 (911) 4002488</t>
+          <t>+7 (911) 4258476</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Багреева Мария Викторовна</t>
+          <t>Каштанова Анна Геннадиевна</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Сайкл разовое без клубной карты</t>
+          <t>Сайкл разовое при наличии клубной карты</t>
         </is>
       </c>
       <c r="F487" s="22" t="n">
-        <v>46034</v>
+        <v>46135</v>
       </c>
       <c r="G487" s="22" t="n">
-        <v>46034</v>
+        <v>46135</v>
       </c>
       <c r="H487" s="22" t="n">
-        <v>46034</v>
+        <v>46135</v>
       </c>
       <c r="I487" s="22" t="n">
-        <v>46034</v>
+        <v>46135</v>
       </c>
       <c r="J487" t="n">
         <v>1</v>
@@ -30052,10 +30052,10 @@
         <v>0</v>
       </c>
       <c r="L487" t="n">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="M487" t="n">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="N487" t="n">
         <v>0</v>
@@ -30067,47 +30067,47 @@
       </c>
       <c r="P487" t="inlineStr">
         <is>
-          <t>Абраамян Татьяна Викторовна</t>
+          <t>Васильева Яна Денисовна</t>
         </is>
       </c>
     </row>
     <row r="488" ht="15.75" customHeight="1" s="21">
       <c r="A488" t="inlineStr">
         <is>
-          <t>00000022640-1</t>
+          <t>00000024163-1</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>000073547</t>
+          <t>000017765</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>+7 (953) 5280283</t>
+          <t>+7 (911) 4332915</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Сторожева Кира Алексеевна</t>
+          <t>Каракай Ольга Сергеевна</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Сайкл разовое без клубной карты</t>
+          <t>Сайкл разовое при наличии клубной карты</t>
         </is>
       </c>
       <c r="F488" s="22" t="n">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="G488" s="22" t="n">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="H488" s="22" t="n">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="I488" s="22" t="n">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="J488" t="n">
         <v>1</v>
@@ -30116,10 +30116,10 @@
         <v>0</v>
       </c>
       <c r="L488" t="n">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="M488" t="n">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="N488" t="n">
         <v>0</v>
@@ -30138,22 +30138,22 @@
     <row r="489" ht="15.75" customHeight="1" s="21">
       <c r="A489" t="inlineStr">
         <is>
-          <t>00000024034-1</t>
+          <t>00000024340-1</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>000007367</t>
+          <t>000020994</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>+7 (911) 4258476</t>
+          <t>+7 (911) 4068867</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Каштанова Анна Геннадиевна</t>
+          <t>Артемьева Елена Евгеньевна</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -30162,16 +30162,16 @@
         </is>
       </c>
       <c r="F489" s="22" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="G489" s="22" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="H489" s="22" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="I489" s="22" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="J489" t="n">
         <v>1</v>
@@ -30195,29 +30195,29 @@
       </c>
       <c r="P489" t="inlineStr">
         <is>
-          <t>Васильева Яна Денисовна</t>
+          <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
     </row>
     <row r="490" ht="15.75" customHeight="1" s="21">
       <c r="A490" t="inlineStr">
         <is>
-          <t>00000024163-1</t>
+          <t>00000024169-1</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>000017765</t>
+          <t>000068490</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>+7 (911) 4332915</t>
+          <t>+7 (911) 4103222</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Каракай Ольга Сергеевна</t>
+          <t>Филиппова Наталья Владимировна</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -30254,34 +30254,34 @@
       </c>
       <c r="O490" t="inlineStr">
         <is>
-          <t>сбп</t>
+          <t>безналичные</t>
         </is>
       </c>
       <c r="P490" t="inlineStr">
         <is>
-          <t>Пеуна Анастасия Ивановна</t>
+          <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
     </row>
     <row r="491" ht="15.75" customHeight="1" s="21">
       <c r="A491" t="inlineStr">
         <is>
-          <t>00000024340-1</t>
+          <t>00000024170-1</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>000020994</t>
+          <t>000068553</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>+7 (911) 4068867</t>
+          <t>+7 (921) 6288212</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Артемьева Елена Евгеньевна</t>
+          <t>Шарпарь Лариса Анатольевна</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -30290,16 +30290,16 @@
         </is>
       </c>
       <c r="F491" s="22" t="n">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="G491" s="22" t="n">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="H491" s="22" t="n">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="I491" s="22" t="n">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="J491" t="n">
         <v>1</v>
@@ -30330,52 +30330,52 @@
     <row r="492" ht="15.75" customHeight="1" s="21">
       <c r="A492" t="inlineStr">
         <is>
-          <t>00000024169-1</t>
+          <t>00000028788-1</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>000068490</t>
+          <t>000019415</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>+7 (911) 4103222</t>
+          <t>+7 (921) 0119777</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Филиппова Наталья Владимировна</t>
+          <t>Цымбал Татьяна Евгеньевна</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Сайкл разовое при наличии клубной карты</t>
+          <t>Солярий 1 минута</t>
         </is>
       </c>
       <c r="F492" s="22" t="n">
-        <v>46135</v>
+        <v>46158</v>
       </c>
       <c r="G492" s="22" t="n">
-        <v>46135</v>
+        <v>46158</v>
       </c>
       <c r="H492" s="22" t="n">
-        <v>46135</v>
+        <v>46158</v>
       </c>
       <c r="I492" s="22" t="n">
-        <v>46135</v>
+        <v>46158</v>
       </c>
       <c r="J492" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K492" t="n">
         <v>0</v>
       </c>
       <c r="L492" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="M492" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="N492" t="n">
         <v>0</v>
@@ -30387,59 +30387,59 @@
       </c>
       <c r="P492" t="inlineStr">
         <is>
-          <t>Абраамян Татьяна Викторовна</t>
+          <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
     </row>
     <row r="493" ht="15.75" customHeight="1" s="21">
       <c r="A493" t="inlineStr">
         <is>
-          <t>00000024170-1</t>
+          <t>00000029404-1</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>000068553</t>
+          <t>000023034</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>+7 (921) 6288212</t>
+          <t>+7 (911) 4270228, +7 (911) 4094143</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Шарпарь Лариса Анатольевна</t>
+          <t>Марина Татьяна Сергеевна</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Сайкл разовое при наличии клубной карты</t>
+          <t>Солярий 1 минута</t>
         </is>
       </c>
       <c r="F493" s="22" t="n">
-        <v>46135</v>
+        <v>46162</v>
       </c>
       <c r="G493" s="22" t="n">
-        <v>46135</v>
+        <v>46162</v>
       </c>
       <c r="H493" s="22" t="n">
-        <v>46135</v>
+        <v>46162</v>
       </c>
       <c r="I493" s="22" t="n">
-        <v>46135</v>
+        <v>46162</v>
       </c>
       <c r="J493" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K493" t="n">
         <v>0</v>
       </c>
       <c r="L493" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="M493" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="N493" t="n">
         <v>0</v>
@@ -30451,29 +30451,29 @@
       </c>
       <c r="P493" t="inlineStr">
         <is>
-          <t>Абраамян Татьяна Викторовна</t>
+          <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
     </row>
     <row r="494" ht="15.75" customHeight="1" s="21">
       <c r="A494" t="inlineStr">
         <is>
-          <t>00000028788-1</t>
+          <t>00000027577-1</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>000019415</t>
+          <t>000051772</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>+7 (921) 0119777</t>
+          <t>+7 (921) 5230651</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Цымбал Татьяна Евгеньевна</t>
+          <t>Хабазова Полина Васильевна</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -30482,16 +30482,16 @@
         </is>
       </c>
       <c r="F494" s="22" t="n">
-        <v>46158</v>
+        <v>46152</v>
       </c>
       <c r="G494" s="22" t="n">
-        <v>46158</v>
+        <v>46152</v>
       </c>
       <c r="H494" s="22" t="n">
-        <v>46158</v>
+        <v>46152</v>
       </c>
       <c r="I494" s="22" t="n">
-        <v>46158</v>
+        <v>46152</v>
       </c>
       <c r="J494" t="n">
         <v>5</v>
@@ -30515,29 +30515,29 @@
       </c>
       <c r="P494" t="inlineStr">
         <is>
-          <t>Пилия Анастасия Артуровна</t>
+          <t>Васильева Яна Денисовна</t>
         </is>
       </c>
     </row>
     <row r="495" ht="15.75" customHeight="1" s="21">
       <c r="A495" t="inlineStr">
         <is>
-          <t>00000029404-1</t>
+          <t>00000029379-1</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>000023034</t>
+          <t>000059707</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>+7 (911) 4270228, +7 (911) 4094143</t>
+          <t>+7 (963) 7457171</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Марина Татьяна Сергеевна</t>
+          <t>Климова Полина Сергеевна</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -30579,29 +30579,29 @@
       </c>
       <c r="P495" t="inlineStr">
         <is>
-          <t>Пеуна Анастасия Ивановна</t>
+          <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
     </row>
     <row r="496" ht="15.75" customHeight="1" s="21">
       <c r="A496" t="inlineStr">
         <is>
-          <t>00000027577-1</t>
+          <t>00000028353-1</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>000051772</t>
+          <t>000067845</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>+7 (921) 5230651</t>
+          <t>+7 (911) 4088363</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Хабазова Полина Васильевна</t>
+          <t>Стоцкая Юлия Валерьевна</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -30610,28 +30610,28 @@
         </is>
       </c>
       <c r="F496" s="22" t="n">
-        <v>46152</v>
+        <v>46156</v>
       </c>
       <c r="G496" s="22" t="n">
-        <v>46152</v>
+        <v>46156</v>
       </c>
       <c r="H496" s="22" t="n">
-        <v>46152</v>
+        <v>46156</v>
       </c>
       <c r="I496" s="22" t="n">
-        <v>46152</v>
+        <v>46156</v>
       </c>
       <c r="J496" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K496" t="n">
         <v>0</v>
       </c>
       <c r="L496" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="M496" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="N496" t="n">
         <v>0</v>
@@ -30643,50 +30643,50 @@
       </c>
       <c r="P496" t="inlineStr">
         <is>
-          <t>Васильева Яна Денисовна</t>
+          <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
     </row>
     <row r="497" ht="15.75" customHeight="1" s="21">
       <c r="A497" t="inlineStr">
         <is>
-          <t>00000029379-1</t>
+          <t>00000030256-1</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>000059707</t>
+          <t>000019415</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>+7 (963) 7457171</t>
+          <t>+7 (921) 0119777</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>Климова Полина Сергеевна</t>
+          <t>Цымбал Татьяна Евгеньевна</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Солярий 1 минута</t>
+          <t>Солярий 5 минут</t>
         </is>
       </c>
       <c r="F497" s="22" t="n">
-        <v>46162</v>
+        <v>46166</v>
       </c>
       <c r="G497" s="22" t="n">
-        <v>46162</v>
+        <v>46166</v>
       </c>
       <c r="H497" s="22" t="n">
-        <v>46162</v>
+        <v>46166</v>
       </c>
       <c r="I497" s="22" t="n">
-        <v>46162</v>
+        <v>46166</v>
       </c>
       <c r="J497" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K497" t="n">
         <v>0</v>
@@ -30707,59 +30707,59 @@
       </c>
       <c r="P497" t="inlineStr">
         <is>
-          <t>Абраамян Татьяна Викторовна</t>
+          <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
     </row>
     <row r="498" ht="15.75" customHeight="1" s="21">
       <c r="A498" t="inlineStr">
         <is>
-          <t>00000028353-1</t>
+          <t>00000030117-1</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>000067845</t>
+          <t>000029279</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>+7 (911) 4088363</t>
+          <t>+7 (911) 6627953</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Стоцкая Юлия Валерьевна</t>
+          <t>Никонорова Глафира Анатольевна</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Солярий 1 минута</t>
+          <t>Солярий 5 минут</t>
         </is>
       </c>
       <c r="F498" s="22" t="n">
-        <v>46156</v>
+        <v>46165</v>
       </c>
       <c r="G498" s="22" t="n">
-        <v>46156</v>
+        <v>46165</v>
       </c>
       <c r="H498" s="22" t="n">
-        <v>46156</v>
+        <v>46165</v>
       </c>
       <c r="I498" s="22" t="n">
-        <v>46156</v>
+        <v>46165</v>
       </c>
       <c r="J498" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K498" t="n">
         <v>0</v>
       </c>
       <c r="L498" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="M498" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="N498" t="n">
         <v>0</v>
@@ -30771,29 +30771,29 @@
       </c>
       <c r="P498" t="inlineStr">
         <is>
-          <t>Абраамян Татьяна Викторовна</t>
+          <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
     </row>
     <row r="499" ht="15.75" customHeight="1" s="21">
       <c r="A499" t="inlineStr">
         <is>
-          <t>00000030256-1</t>
+          <t>00000030205-1</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>000019415</t>
+          <t>000036898</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>+7 (921) 0119777</t>
+          <t>+7 (921) 4580369, +7 (911) 6684828</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Цымбал Татьяна Евгеньевна</t>
+          <t>Сидоркова Татьяна Александровна</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -30835,29 +30835,29 @@
       </c>
       <c r="P499" t="inlineStr">
         <is>
-          <t>Пилия Анастасия Артуровна</t>
+          <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
     </row>
     <row r="500" ht="15.75" customHeight="1" s="21">
       <c r="A500" t="inlineStr">
         <is>
-          <t>00000030205-1</t>
+          <t>00000030143-1</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>000036898</t>
+          <t>000073187</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>+7 (921) 4580369, +7 (911) 6684828</t>
+          <t>+7 (911) 4266403</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Сидоркова Татьяна Александровна</t>
+          <t>Евсеенкова Светлана Петровна</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -30866,28 +30866,28 @@
         </is>
       </c>
       <c r="F500" s="22" t="n">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="G500" s="22" t="n">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="H500" s="22" t="n">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="I500" s="22" t="n">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="J500" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K500" t="n">
         <v>0</v>
       </c>
       <c r="L500" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="M500" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="N500" t="n">
         <v>0</v>
@@ -30899,29 +30899,29 @@
       </c>
       <c r="P500" t="inlineStr">
         <is>
-          <t>Пеуна Анастасия Ивановна</t>
+          <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
     </row>
     <row r="501" ht="15.75" customHeight="1" s="21">
       <c r="A501" t="inlineStr">
         <is>
-          <t>00000030161-1</t>
+          <t>00000030191-1</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>000071806</t>
+          <t>000073599</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>+7 (911) 4066644</t>
+          <t>+7 (921) 2241613</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Бачев Юрий Александрович</t>
+          <t>Ермолаева Валерия Владимировна</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -30963,59 +30963,59 @@
       </c>
       <c r="P501" t="inlineStr">
         <is>
-          <t>Васильева Яна Денисовна</t>
+          <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
     </row>
     <row r="502" ht="15.75" customHeight="1" s="21">
       <c r="A502" t="inlineStr">
         <is>
-          <t>00000030143-1</t>
+          <t>00000004563-1</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>000073187</t>
+          <t>000015802</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>+7 (911) 4266403</t>
+          <t>+7 (911) 4071349</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Евсеенкова Светлана Петровна</t>
+          <t>Сачунова Валерия Александровна</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Солярий 5 минут</t>
+          <t>Стрип-пластика</t>
         </is>
       </c>
       <c r="F502" s="22" t="n">
-        <v>46165</v>
+        <v>46046</v>
       </c>
       <c r="G502" s="22" t="n">
-        <v>46165</v>
+        <v>46046</v>
       </c>
       <c r="H502" s="22" t="n">
-        <v>46165</v>
+        <v>46046</v>
       </c>
       <c r="I502" s="22" t="n">
-        <v>46165</v>
+        <v>46046</v>
       </c>
       <c r="J502" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K502" t="n">
         <v>0</v>
       </c>
       <c r="L502" t="n">
-        <v>300</v>
+        <v>4500</v>
       </c>
       <c r="M502" t="n">
-        <v>300</v>
+        <v>4500</v>
       </c>
       <c r="N502" t="n">
         <v>0</v>
@@ -31027,59 +31027,59 @@
       </c>
       <c r="P502" t="inlineStr">
         <is>
-          <t>Лисовская Екатерина Александровна</t>
+          <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
     </row>
     <row r="503" ht="15.75" customHeight="1" s="21">
       <c r="A503" t="inlineStr">
         <is>
-          <t>00000030191-1</t>
+          <t>00000004565-1</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>000073599</t>
+          <t>000048218</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>+7 (921) 2241613</t>
+          <t>+7 (911) 4005232</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Ермолаева Валерия Владимировна</t>
+          <t>Прилепская Елена Викторовна</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>Солярий 5 минут</t>
+          <t>Стрип-пластика</t>
         </is>
       </c>
       <c r="F503" s="22" t="n">
-        <v>46166</v>
+        <v>46046</v>
       </c>
       <c r="G503" s="22" t="n">
-        <v>46166</v>
+        <v>46046</v>
       </c>
       <c r="H503" s="22" t="n">
-        <v>46166</v>
+        <v>46046</v>
       </c>
       <c r="I503" s="22" t="n">
-        <v>46166</v>
+        <v>46046</v>
       </c>
       <c r="J503" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K503" t="n">
         <v>0</v>
       </c>
       <c r="L503" t="n">
-        <v>300</v>
+        <v>4500</v>
       </c>
       <c r="M503" t="n">
-        <v>300</v>
+        <v>4500</v>
       </c>
       <c r="N503" t="n">
         <v>0</v>
@@ -31091,29 +31091,29 @@
       </c>
       <c r="P503" t="inlineStr">
         <is>
-          <t>Пилия Анастасия Артуровна</t>
+          <t>Васильева Яна Денисовна</t>
         </is>
       </c>
     </row>
     <row r="504" ht="15.75" customHeight="1" s="21">
       <c r="A504" t="inlineStr">
         <is>
-          <t>00000004563-1</t>
+          <t>00000004568-1</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>000015802</t>
+          <t>000053123</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>+7 (911) 4071349</t>
+          <t>+7 (911) 6650090</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>Сачунова Валерия Александровна</t>
+          <t>Калюка Анна Николаевна</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -31155,29 +31155,29 @@
       </c>
       <c r="P504" t="inlineStr">
         <is>
-          <t>Соколова Анастасия Александровна</t>
+          <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
     </row>
     <row r="505" ht="15.75" customHeight="1" s="21">
       <c r="A505" t="inlineStr">
         <is>
-          <t>00000004565-1</t>
+          <t>00000004579-1</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>000048218</t>
+          <t>000055267</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>+7 (911) 4005232</t>
+          <t>+7 (901) 7619183</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Прилепская Елена Викторовна</t>
+          <t>Иммар Анна Андреевна</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -31219,29 +31219,29 @@
       </c>
       <c r="P505" t="inlineStr">
         <is>
-          <t>Васильева Яна Денисовна</t>
+          <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
     </row>
     <row r="506" ht="15.75" customHeight="1" s="21">
       <c r="A506" t="inlineStr">
         <is>
-          <t>00000004568-1</t>
+          <t>00000004561-1</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>000053123</t>
+          <t>000056500</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>+7 (911) 6650090</t>
+          <t>+7 (911) 6688087, +7 (982) 7568538</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Калюка Анна Николаевна</t>
+          <t>Костомарова Наталья Владимировна</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -31283,47 +31283,47 @@
       </c>
       <c r="P506" t="inlineStr">
         <is>
-          <t>Пилия Анастасия Артуровна</t>
+          <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
     </row>
     <row r="507" ht="15.75" customHeight="1" s="21">
       <c r="A507" t="inlineStr">
         <is>
-          <t>00000004579-1</t>
+          <t>00000076138-1</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>000055267</t>
+          <t>000023964</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>+7 (901) 7619183</t>
+          <t>+7 (911) 4172746, +7 (981) 4039028</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Иммар Анна Андреевна</t>
+          <t>Ивашко Анна Владимировна (Тренер)</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Стрип-пластика</t>
+          <t>Субаренда 1 посещение</t>
         </is>
       </c>
       <c r="F507" s="22" t="n">
-        <v>46046</v>
+        <v>46021</v>
       </c>
       <c r="G507" s="22" t="n">
-        <v>46046</v>
+        <v>46021</v>
       </c>
       <c r="H507" s="22" t="n">
-        <v>46046</v>
+        <v>46021</v>
       </c>
       <c r="I507" s="22" t="n">
-        <v>46046</v>
+        <v>46021</v>
       </c>
       <c r="J507" t="n">
         <v>1</v>
@@ -31332,10 +31332,10 @@
         <v>0</v>
       </c>
       <c r="L507" t="n">
-        <v>4500</v>
+        <v>2000</v>
       </c>
       <c r="M507" t="n">
-        <v>4500</v>
+        <v>2000</v>
       </c>
       <c r="N507" t="n">
         <v>0</v>
@@ -31347,59 +31347,50 @@
       </c>
       <c r="P507" t="inlineStr">
         <is>
-          <t>Мартынова Дарья Дмитриевна</t>
+          <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
     </row>
     <row r="508" ht="15.75" customHeight="1" s="21">
       <c r="A508" t="inlineStr">
         <is>
-          <t>00000004570-1</t>
+          <t>00000001916-2</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>000071137</t>
+          <t>000014428</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>+7 (921) 7289773</t>
+          <t>+7 (911) 4068797</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Карелина Ольга Владимировна</t>
+          <t>Поутанен Ирина Ивановна</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Стрип-пластика</t>
+          <t>Утеря валика</t>
         </is>
       </c>
       <c r="F508" s="22" t="n">
-        <v>46046</v>
+        <v>43844</v>
       </c>
       <c r="G508" s="22" t="n">
-        <v>46046</v>
-      </c>
-      <c r="H508" s="22" t="n">
-        <v>46046</v>
-      </c>
-      <c r="I508" s="22" t="n">
-        <v>46046</v>
+        <v>43845</v>
       </c>
       <c r="J508" t="n">
         <v>1</v>
       </c>
-      <c r="K508" t="n">
-        <v>0</v>
-      </c>
       <c r="L508" t="n">
-        <v>4500</v>
+        <v>500</v>
       </c>
       <c r="M508" t="n">
-        <v>4500</v>
+        <v>500</v>
       </c>
       <c r="N508" t="n">
         <v>0</v>
@@ -31411,47 +31402,47 @@
       </c>
       <c r="P508" t="inlineStr">
         <is>
-          <t>Фёдорова Надежда Сергеевна</t>
+          <t>УТОЧНИТЬ: вне import_заявки</t>
         </is>
       </c>
     </row>
     <row r="509" ht="15.75" customHeight="1" s="21">
       <c r="A509" t="inlineStr">
         <is>
-          <t>00000007846-1</t>
+          <t>00000002498-1</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>000036376</t>
+          <t>000016735</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>+7 (911) 4093061</t>
+          <t>+7 (911) 4024926</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Шипулова Вероника (Тренер)</t>
+          <t>Соколов Василий Юрьевич</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>Субаренда 1 посещение</t>
+          <t>Утеря ключа от шкафчика</t>
         </is>
       </c>
       <c r="F509" s="22" t="n">
-        <v>46060</v>
+        <v>46037</v>
       </c>
       <c r="G509" s="22" t="n">
-        <v>46060</v>
+        <v>46037</v>
       </c>
       <c r="H509" s="22" t="n">
-        <v>46060</v>
+        <v>46037</v>
       </c>
       <c r="I509" s="22" t="n">
-        <v>46060</v>
+        <v>46037</v>
       </c>
       <c r="J509" t="n">
         <v>1</v>
@@ -31460,10 +31451,10 @@
         <v>0</v>
       </c>
       <c r="L509" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="M509" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="N509" t="n">
         <v>0</v>
@@ -31475,47 +31466,47 @@
       </c>
       <c r="P509" t="inlineStr">
         <is>
-          <t>Пилия Анастасия Артуровна</t>
+          <t>Васильева Яна Денисовна</t>
         </is>
       </c>
     </row>
     <row r="510" ht="15.75" customHeight="1" s="21">
       <c r="A510" t="inlineStr">
         <is>
-          <t>00000008369-1</t>
+          <t>00000071923-1</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>000036376</t>
+          <t>000019105</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>+7 (911) 4093061</t>
+          <t>+7 (909) 5711729</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Шипулова Вероника (Тренер)</t>
+          <t>Харькин Павел Викторович</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Субаренда 1 посещение</t>
+          <t>Утеря ключа от шкафчика</t>
         </is>
       </c>
       <c r="F510" s="22" t="n">
-        <v>46063</v>
+        <v>46000</v>
       </c>
       <c r="G510" s="22" t="n">
-        <v>46063</v>
+        <v>46000</v>
       </c>
       <c r="H510" s="22" t="n">
-        <v>46063</v>
+        <v>46000</v>
       </c>
       <c r="I510" s="22" t="n">
-        <v>46063</v>
+        <v>46000</v>
       </c>
       <c r="J510" t="n">
         <v>1</v>
@@ -31524,10 +31515,10 @@
         <v>0</v>
       </c>
       <c r="L510" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="M510" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="N510" t="n">
         <v>0</v>
@@ -31539,47 +31530,47 @@
       </c>
       <c r="P510" t="inlineStr">
         <is>
-          <t>Пилия Анастасия Артуровна</t>
+          <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
     </row>
     <row r="511" ht="15.75" customHeight="1" s="21">
       <c r="A511" t="inlineStr">
         <is>
-          <t>00000008806-1</t>
+          <t>00000006953-1</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>000036376</t>
+          <t>000064277</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>+7 (911) 4093061</t>
+          <t>+7 (921) 4266626</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>Шипулова Вероника (Тренер)</t>
+          <t>Рюппиев Максим Александрович</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Субаренда 1 посещение</t>
+          <t>Утеря ключа от шкафчика</t>
         </is>
       </c>
       <c r="F511" s="22" t="n">
-        <v>46065</v>
+        <v>45690</v>
       </c>
       <c r="G511" s="22" t="n">
-        <v>46065</v>
+        <v>45690</v>
       </c>
       <c r="H511" s="22" t="n">
-        <v>46065</v>
+        <v>45690</v>
       </c>
       <c r="I511" s="22" t="n">
-        <v>46065</v>
+        <v>45690</v>
       </c>
       <c r="J511" t="n">
         <v>1</v>
@@ -31588,10 +31579,10 @@
         <v>0</v>
       </c>
       <c r="L511" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="M511" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="N511" t="n">
         <v>0</v>
@@ -31603,47 +31594,47 @@
       </c>
       <c r="P511" t="inlineStr">
         <is>
-          <t>Пилия Анастасия Артуровна</t>
+          <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
     </row>
     <row r="512" ht="15.75" customHeight="1" s="21">
       <c r="A512" t="inlineStr">
         <is>
-          <t>00000009309-1</t>
+          <t>00000070699-1</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>000036376</t>
+          <t>000064982</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>+7 (911) 4093061</t>
+          <t>+7 (965) 0640893</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>Шипулова Вероника (Тренер)</t>
+          <t>Куканов Илья Александрович</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Субаренда 1 посещение</t>
+          <t>Утеря ключа от шкафчика</t>
         </is>
       </c>
       <c r="F512" s="22" t="n">
-        <v>46067</v>
+        <v>45995</v>
       </c>
       <c r="G512" s="22" t="n">
-        <v>46067</v>
+        <v>45995</v>
       </c>
       <c r="H512" s="22" t="n">
-        <v>46067</v>
+        <v>45995</v>
       </c>
       <c r="I512" s="22" t="n">
-        <v>46067</v>
+        <v>45995</v>
       </c>
       <c r="J512" t="n">
         <v>1</v>
@@ -31652,10 +31643,10 @@
         <v>0</v>
       </c>
       <c r="L512" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="M512" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="N512" t="n">
         <v>0</v>
@@ -31674,40 +31665,40 @@
     <row r="513" ht="15.75" customHeight="1" s="21">
       <c r="A513" t="inlineStr">
         <is>
-          <t>00000008345-1</t>
+          <t>00000019958-1</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>000053259</t>
+          <t>000072969</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>+7 (921) 0127074, +7 (925) 5548982</t>
+          <t>+7 (922) 6618306</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>Черкасов Иван Алексеевич (Сотрудник)</t>
+          <t>Малинаускене Анастасия Дмитриевна</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Субаренда 1 посещение</t>
+          <t>Утеря ключа от шкафчика</t>
         </is>
       </c>
       <c r="F513" s="22" t="n">
-        <v>46063</v>
+        <v>46115</v>
       </c>
       <c r="G513" s="22" t="n">
-        <v>46063</v>
+        <v>46115</v>
       </c>
       <c r="H513" s="22" t="n">
-        <v>46063</v>
+        <v>46115</v>
       </c>
       <c r="I513" s="22" t="n">
-        <v>46063</v>
+        <v>46115</v>
       </c>
       <c r="J513" t="n">
         <v>1</v>
@@ -31716,10 +31707,10 @@
         <v>0</v>
       </c>
       <c r="L513" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="M513" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="N513" t="n">
         <v>0</v>
@@ -31731,50 +31722,59 @@
       </c>
       <c r="P513" t="inlineStr">
         <is>
-          <t>Васильева Яна Денисовна</t>
+          <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
     </row>
     <row r="514" ht="15.75" customHeight="1" s="21">
       <c r="A514" t="inlineStr">
         <is>
-          <t>00000001916-2</t>
+          <t>00000066885-1</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>000014428</t>
+          <t>000000166</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>+7 (911) 4068797</t>
+          <t>+7 (953) 5370893, +7 (981) 4026753</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>Поутанен Ирина Ивановна</t>
+          <t>Агафонов Александр Сергеевич</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>Утеря валика</t>
+          <t>Утеря магнитного ключа-метки</t>
         </is>
       </c>
       <c r="F514" s="22" t="n">
-        <v>43844</v>
+        <v>45638</v>
       </c>
       <c r="G514" s="22" t="n">
-        <v>43845</v>
+        <v>45638</v>
+      </c>
+      <c r="H514" s="22" t="n">
+        <v>45638</v>
+      </c>
+      <c r="I514" s="22" t="n">
+        <v>45638</v>
       </c>
       <c r="J514" t="n">
         <v>1</v>
       </c>
+      <c r="K514" t="n">
+        <v>0</v>
+      </c>
       <c r="L514" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="M514" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="N514" t="n">
         <v>0</v>
@@ -31786,47 +31786,47 @@
       </c>
       <c r="P514" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: вне import_заявки</t>
+          <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
     </row>
     <row r="515" ht="15.75" customHeight="1" s="21">
       <c r="A515" t="inlineStr">
         <is>
-          <t>00000002498-1</t>
+          <t>00000033882-1</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>000016735</t>
+          <t>000059719</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>+7 (911) 4024926</t>
+          <t>+7 (909) 5698181</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>Соколов Василий Юрьевич</t>
+          <t>Казарян Анна Хачиковна</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>Утеря ключа от шкафчика</t>
+          <t>Утеря магнитного ключа-метки</t>
         </is>
       </c>
       <c r="F515" s="22" t="n">
-        <v>46037</v>
+        <v>45465</v>
       </c>
       <c r="G515" s="22" t="n">
-        <v>46037</v>
+        <v>45465</v>
       </c>
       <c r="H515" s="22" t="n">
-        <v>46037</v>
+        <v>45465</v>
       </c>
       <c r="I515" s="22" t="n">
-        <v>46037</v>
+        <v>45465</v>
       </c>
       <c r="J515" t="n">
         <v>1</v>
@@ -31835,10 +31835,10 @@
         <v>0</v>
       </c>
       <c r="L515" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="M515" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="N515" t="n">
         <v>0</v>
@@ -31850,47 +31850,47 @@
       </c>
       <c r="P515" t="inlineStr">
         <is>
-          <t>Васильева Яна Денисовна</t>
+          <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
     </row>
     <row r="516" ht="15.75" customHeight="1" s="21">
       <c r="A516" t="inlineStr">
         <is>
-          <t>00000071923-1</t>
+          <t>00000029120-1</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>000019105</t>
+          <t>000063847</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>+7 (909) 5711729</t>
+          <t>+7 (968) 0593556</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>Харькин Павел Викторович</t>
+          <t>Бахтиева Ильмира Ильшатовна</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Утеря ключа от шкафчика</t>
+          <t>Утеря магнитного ключа-метки</t>
         </is>
       </c>
       <c r="F516" s="22" t="n">
-        <v>46000</v>
+        <v>45435</v>
       </c>
       <c r="G516" s="22" t="n">
-        <v>46000</v>
+        <v>45435</v>
       </c>
       <c r="H516" s="22" t="n">
-        <v>46000</v>
+        <v>45435</v>
       </c>
       <c r="I516" s="22" t="n">
-        <v>46000</v>
+        <v>45435</v>
       </c>
       <c r="J516" t="n">
         <v>1</v>
@@ -31899,10 +31899,10 @@
         <v>0</v>
       </c>
       <c r="L516" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="M516" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="N516" t="n">
         <v>0</v>
@@ -31914,47 +31914,47 @@
       </c>
       <c r="P516" t="inlineStr">
         <is>
-          <t>Абраамян Татьяна Викторовна</t>
+          <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
     </row>
     <row r="517" ht="15.75" customHeight="1" s="21">
       <c r="A517" t="inlineStr">
         <is>
-          <t>00000006953-1</t>
+          <t>00000007886-1</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>000064277</t>
+          <t>000066870</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>+7 (921) 4266626</t>
+          <t>+7 (999) 1770543</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>Рюппиев Максим Александрович</t>
+          <t>Mesvaniya Devanshu Pfagneshbhai</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>Утеря ключа от шкафчика</t>
+          <t>Утеря магнитного ключа-метки</t>
         </is>
       </c>
       <c r="F517" s="22" t="n">
-        <v>45690</v>
+        <v>45694</v>
       </c>
       <c r="G517" s="22" t="n">
-        <v>45690</v>
+        <v>45694</v>
       </c>
       <c r="H517" s="22" t="n">
-        <v>45690</v>
+        <v>45694</v>
       </c>
       <c r="I517" s="22" t="n">
-        <v>45690</v>
+        <v>45694</v>
       </c>
       <c r="J517" t="n">
         <v>1</v>
@@ -31963,10 +31963,10 @@
         <v>0</v>
       </c>
       <c r="L517" t="n">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="M517" t="n">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="N517" t="n">
         <v>0</v>
@@ -31978,47 +31978,47 @@
       </c>
       <c r="P517" t="inlineStr">
         <is>
-          <t>Абраамян Татьяна Викторовна</t>
+          <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
     </row>
     <row r="518" ht="15.75" customHeight="1" s="21">
       <c r="A518" t="inlineStr">
         <is>
-          <t>00000070699-1</t>
+          <t>00000019958-2</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>000064982</t>
+          <t>000072969</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>+7 (965) 0640893</t>
+          <t>+7 (922) 6618306</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>Куканов Илья Александрович</t>
+          <t>Малинаускене Анастасия Дмитриевна</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Утеря ключа от шкафчика</t>
+          <t>Утеря магнитного ключа-метки</t>
         </is>
       </c>
       <c r="F518" s="22" t="n">
-        <v>45995</v>
+        <v>46115</v>
       </c>
       <c r="G518" s="22" t="n">
-        <v>45995</v>
+        <v>46115</v>
       </c>
       <c r="H518" s="22" t="n">
-        <v>45995</v>
+        <v>46115</v>
       </c>
       <c r="I518" s="22" t="n">
-        <v>45995</v>
+        <v>46115</v>
       </c>
       <c r="J518" t="n">
         <v>1</v>
@@ -32027,10 +32027,10 @@
         <v>0</v>
       </c>
       <c r="L518" t="n">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="M518" t="n">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="N518" t="n">
         <v>0</v>
@@ -32049,40 +32049,40 @@
     <row r="519" ht="15.75" customHeight="1" s="21">
       <c r="A519" t="inlineStr">
         <is>
-          <t>00000019958-1</t>
+          <t>00000067106-1</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>000072969</t>
+          <t>000053627</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>+7 (922) 6618306</t>
+          <t>+7 (981) 4339515</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>Малинаускене Анастасия Дмитриевна</t>
+          <t>Оглоблина Вероника Игоревна</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Утеря ключа от шкафчика</t>
+          <t>Утеря манжеты</t>
         </is>
       </c>
       <c r="F519" s="22" t="n">
-        <v>46115</v>
+        <v>44916</v>
       </c>
       <c r="G519" s="22" t="n">
-        <v>46115</v>
+        <v>44916</v>
       </c>
       <c r="H519" s="22" t="n">
-        <v>46115</v>
+        <v>44916</v>
       </c>
       <c r="I519" s="22" t="n">
-        <v>46115</v>
+        <v>44916</v>
       </c>
       <c r="J519" t="n">
         <v>1</v>
@@ -32091,10 +32091,10 @@
         <v>0</v>
       </c>
       <c r="L519" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="M519" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="N519" t="n">
         <v>0</v>
@@ -32106,47 +32106,47 @@
       </c>
       <c r="P519" t="inlineStr">
         <is>
-          <t>Пилия Анастасия Артуровна</t>
+          <t>Васильева Яна Денисовна</t>
         </is>
       </c>
     </row>
     <row r="520" ht="15.75" customHeight="1" s="21">
       <c r="A520" t="inlineStr">
         <is>
-          <t>00000066885-1</t>
+          <t>00000014426-1</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>000000166</t>
+          <t>000020245</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>+7 (953) 5370893, +7 (981) 4026753</t>
+          <t>+7 (953) 5392759</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>Агафонов Александр Сергеевич</t>
+          <t>Шкадрович Игорь Геннадьевич</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>Утеря магнитного ключа-метки</t>
+          <t>Утеря номерка от гардероба</t>
         </is>
       </c>
       <c r="F520" s="22" t="n">
-        <v>45638</v>
+        <v>46090</v>
       </c>
       <c r="G520" s="22" t="n">
-        <v>45638</v>
+        <v>46090</v>
       </c>
       <c r="H520" s="22" t="n">
-        <v>45638</v>
+        <v>46090</v>
       </c>
       <c r="I520" s="22" t="n">
-        <v>45638</v>
+        <v>46090</v>
       </c>
       <c r="J520" t="n">
         <v>1</v>
@@ -32155,10 +32155,10 @@
         <v>0</v>
       </c>
       <c r="L520" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="M520" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="N520" t="n">
         <v>0</v>
@@ -32170,47 +32170,47 @@
       </c>
       <c r="P520" t="inlineStr">
         <is>
-          <t>Пилия Анастасия Артуровна</t>
+          <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
     </row>
     <row r="521" ht="15.75" customHeight="1" s="21">
       <c r="A521" t="inlineStr">
         <is>
-          <t>00000033882-1</t>
+          <t>00000014115-1</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>000059719</t>
+          <t>000034520</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>+7 (909) 5698181</t>
+          <t>+7 (911) 4192568</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>Казарян Анна Хачиковна</t>
+          <t>Матвеева Анна Юрьевна</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>Утеря магнитного ключа-метки</t>
+          <t>Утеря номерка от гардероба</t>
         </is>
       </c>
       <c r="F521" s="22" t="n">
-        <v>45465</v>
+        <v>46088</v>
       </c>
       <c r="G521" s="22" t="n">
-        <v>45465</v>
+        <v>46088</v>
       </c>
       <c r="H521" s="22" t="n">
-        <v>45465</v>
+        <v>46088</v>
       </c>
       <c r="I521" s="22" t="n">
-        <v>45465</v>
+        <v>46088</v>
       </c>
       <c r="J521" t="n">
         <v>1</v>
@@ -32219,10 +32219,10 @@
         <v>0</v>
       </c>
       <c r="L521" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="M521" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="N521" t="n">
         <v>0</v>
@@ -32241,40 +32241,40 @@
     <row r="522" ht="15.75" customHeight="1" s="21">
       <c r="A522" t="inlineStr">
         <is>
-          <t>00000029120-1</t>
+          <t>00000023718-1</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>000063847</t>
+          <t>000059409</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>+7 (968) 0593556</t>
+          <t>+7 (921) 0180911</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>Бахтиева Ильмира Ильшатовна</t>
+          <t>Лысенко Екатерина Анатольевна</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>Утеря магнитного ключа-метки</t>
+          <t>Утеря номерка от гардероба</t>
         </is>
       </c>
       <c r="F522" s="22" t="n">
-        <v>45435</v>
+        <v>46133</v>
       </c>
       <c r="G522" s="22" t="n">
-        <v>45435</v>
+        <v>46133</v>
       </c>
       <c r="H522" s="22" t="n">
-        <v>45435</v>
+        <v>46133</v>
       </c>
       <c r="I522" s="22" t="n">
-        <v>45435</v>
+        <v>46133</v>
       </c>
       <c r="J522" t="n">
         <v>1</v>
@@ -32283,10 +32283,10 @@
         <v>0</v>
       </c>
       <c r="L522" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="M522" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="N522" t="n">
         <v>0</v>
@@ -32298,47 +32298,47 @@
       </c>
       <c r="P522" t="inlineStr">
         <is>
-          <t>Пилия Анастасия Артуровна</t>
+          <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
     </row>
     <row r="523" ht="15.75" customHeight="1" s="21">
       <c r="A523" t="inlineStr">
         <is>
-          <t>00000007886-1</t>
+          <t>00000018566-1</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>000066870</t>
+          <t>000060039</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>+7 (999) 1770543</t>
+          <t>+7 (911) 4434212</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>Mesvaniya Devanshu Pfagneshbhai</t>
+          <t>Ливандовская Анна Александровна</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>Утеря магнитного ключа-метки</t>
+          <t>Утеря номерка от гардероба</t>
         </is>
       </c>
       <c r="F523" s="22" t="n">
-        <v>45694</v>
+        <v>46108</v>
       </c>
       <c r="G523" s="22" t="n">
-        <v>45694</v>
+        <v>46108</v>
       </c>
       <c r="H523" s="22" t="n">
-        <v>45694</v>
+        <v>46108</v>
       </c>
       <c r="I523" s="22" t="n">
-        <v>45694</v>
+        <v>46108</v>
       </c>
       <c r="J523" t="n">
         <v>1</v>
@@ -32347,10 +32347,10 @@
         <v>0</v>
       </c>
       <c r="L523" t="n">
-        <v>1300</v>
+        <v>200</v>
       </c>
       <c r="M523" t="n">
-        <v>1300</v>
+        <v>200</v>
       </c>
       <c r="N523" t="n">
         <v>0</v>
@@ -32362,47 +32362,47 @@
       </c>
       <c r="P523" t="inlineStr">
         <is>
-          <t>Яковлева Александра Владимировна</t>
+          <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
     </row>
     <row r="524" ht="15.75" customHeight="1" s="21">
       <c r="A524" t="inlineStr">
         <is>
-          <t>00000019958-2</t>
+          <t>00000022030-1</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>000072969</t>
+          <t>000073471</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>+7 (922) 6618306</t>
+          <t>+7 (921) 2291023</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>Малинаускене Анастасия Дмитриевна</t>
+          <t>Гжималаускене Анна Сергеевна</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>Утеря магнитного ключа-метки</t>
+          <t>Утеря номерка от гардероба</t>
         </is>
       </c>
       <c r="F524" s="22" t="n">
-        <v>46115</v>
+        <v>46125</v>
       </c>
       <c r="G524" s="22" t="n">
-        <v>46115</v>
+        <v>46125</v>
       </c>
       <c r="H524" s="22" t="n">
-        <v>46115</v>
+        <v>46125</v>
       </c>
       <c r="I524" s="22" t="n">
-        <v>46115</v>
+        <v>46125</v>
       </c>
       <c r="J524" t="n">
         <v>1</v>
@@ -32411,10 +32411,10 @@
         <v>0</v>
       </c>
       <c r="L524" t="n">
-        <v>1300</v>
+        <v>200</v>
       </c>
       <c r="M524" t="n">
-        <v>1300</v>
+        <v>200</v>
       </c>
       <c r="N524" t="n">
         <v>0</v>
@@ -32426,394 +32426,16 @@
       </c>
       <c r="P524" t="inlineStr">
         <is>
-          <t>Пилия Анастасия Артуровна</t>
-        </is>
-      </c>
-    </row>
-    <row r="525" ht="15.75" customHeight="1" s="21">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>00000067106-1</t>
-        </is>
-      </c>
-      <c r="B525" t="inlineStr">
-        <is>
-          <t>000053627</t>
-        </is>
-      </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>+7 (981) 4339515</t>
-        </is>
-      </c>
-      <c r="D525" t="inlineStr">
-        <is>
-          <t>Оглоблина Вероника Игоревна</t>
-        </is>
-      </c>
-      <c r="E525" t="inlineStr">
-        <is>
-          <t>Утеря манжеты</t>
-        </is>
-      </c>
-      <c r="F525" s="22" t="n">
-        <v>44916</v>
-      </c>
-      <c r="G525" s="22" t="n">
-        <v>44916</v>
-      </c>
-      <c r="H525" s="22" t="n">
-        <v>44916</v>
-      </c>
-      <c r="I525" s="22" t="n">
-        <v>44916</v>
-      </c>
-      <c r="J525" t="n">
-        <v>1</v>
-      </c>
-      <c r="K525" t="n">
-        <v>0</v>
-      </c>
-      <c r="L525" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M525" t="n">
-        <v>1000</v>
-      </c>
-      <c r="N525" t="n">
-        <v>0</v>
-      </c>
-      <c r="O525" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
-      </c>
-      <c r="P525" t="inlineStr">
-        <is>
-          <t>Васильева Яна Денисовна</t>
-        </is>
-      </c>
-    </row>
-    <row r="526" ht="15.75" customHeight="1" s="21">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>00000014426-1</t>
-        </is>
-      </c>
-      <c r="B526" t="inlineStr">
-        <is>
-          <t>000020245</t>
-        </is>
-      </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>+7 (953) 5392759</t>
-        </is>
-      </c>
-      <c r="D526" t="inlineStr">
-        <is>
-          <t>Шкадрович Игорь Геннадьевич</t>
-        </is>
-      </c>
-      <c r="E526" t="inlineStr">
-        <is>
-          <t>Утеря номерка от гардероба</t>
-        </is>
-      </c>
-      <c r="F526" s="22" t="n">
-        <v>46090</v>
-      </c>
-      <c r="G526" s="22" t="n">
-        <v>46090</v>
-      </c>
-      <c r="H526" s="22" t="n">
-        <v>46090</v>
-      </c>
-      <c r="I526" s="22" t="n">
-        <v>46090</v>
-      </c>
-      <c r="J526" t="n">
-        <v>1</v>
-      </c>
-      <c r="K526" t="n">
-        <v>0</v>
-      </c>
-      <c r="L526" t="n">
-        <v>200</v>
-      </c>
-      <c r="M526" t="n">
-        <v>200</v>
-      </c>
-      <c r="N526" t="n">
-        <v>0</v>
-      </c>
-      <c r="O526" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
-      </c>
-      <c r="P526" t="inlineStr">
-        <is>
-          <t>Пеуна Анастасия Ивановна</t>
-        </is>
-      </c>
-    </row>
-    <row r="527" ht="15.75" customHeight="1" s="21">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>00000014115-1</t>
-        </is>
-      </c>
-      <c r="B527" t="inlineStr">
-        <is>
-          <t>000034520</t>
-        </is>
-      </c>
-      <c r="C527" t="inlineStr">
-        <is>
-          <t>+7 (911) 4192568</t>
-        </is>
-      </c>
-      <c r="D527" t="inlineStr">
-        <is>
-          <t>Матвеева Анна Юрьевна</t>
-        </is>
-      </c>
-      <c r="E527" t="inlineStr">
-        <is>
-          <t>Утеря номерка от гардероба</t>
-        </is>
-      </c>
-      <c r="F527" s="22" t="n">
-        <v>46088</v>
-      </c>
-      <c r="G527" s="22" t="n">
-        <v>46088</v>
-      </c>
-      <c r="H527" s="22" t="n">
-        <v>46088</v>
-      </c>
-      <c r="I527" s="22" t="n">
-        <v>46088</v>
-      </c>
-      <c r="J527" t="n">
-        <v>1</v>
-      </c>
-      <c r="K527" t="n">
-        <v>0</v>
-      </c>
-      <c r="L527" t="n">
-        <v>200</v>
-      </c>
-      <c r="M527" t="n">
-        <v>200</v>
-      </c>
-      <c r="N527" t="n">
-        <v>0</v>
-      </c>
-      <c r="O527" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
-      </c>
-      <c r="P527" t="inlineStr">
-        <is>
-          <t>Пеуна Анастасия Ивановна</t>
-        </is>
-      </c>
-    </row>
-    <row r="528" ht="15.75" customHeight="1" s="21">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>00000023718-1</t>
-        </is>
-      </c>
-      <c r="B528" t="inlineStr">
-        <is>
-          <t>000059409</t>
-        </is>
-      </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>+7 (921) 0180911</t>
-        </is>
-      </c>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>Лысенко Екатерина Анатольевна</t>
-        </is>
-      </c>
-      <c r="E528" t="inlineStr">
-        <is>
-          <t>Утеря номерка от гардероба</t>
-        </is>
-      </c>
-      <c r="F528" s="22" t="n">
-        <v>46133</v>
-      </c>
-      <c r="G528" s="22" t="n">
-        <v>46133</v>
-      </c>
-      <c r="H528" s="22" t="n">
-        <v>46133</v>
-      </c>
-      <c r="I528" s="22" t="n">
-        <v>46133</v>
-      </c>
-      <c r="J528" t="n">
-        <v>1</v>
-      </c>
-      <c r="K528" t="n">
-        <v>0</v>
-      </c>
-      <c r="L528" t="n">
-        <v>200</v>
-      </c>
-      <c r="M528" t="n">
-        <v>200</v>
-      </c>
-      <c r="N528" t="n">
-        <v>0</v>
-      </c>
-      <c r="O528" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
-      </c>
-      <c r="P528" t="inlineStr">
-        <is>
-          <t>Соколова Анастасия Александровна</t>
-        </is>
-      </c>
-    </row>
-    <row r="529" ht="15.75" customHeight="1" s="21">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>00000018566-1</t>
-        </is>
-      </c>
-      <c r="B529" t="inlineStr">
-        <is>
-          <t>000060039</t>
-        </is>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>+7 (911) 4434212</t>
-        </is>
-      </c>
-      <c r="D529" t="inlineStr">
-        <is>
-          <t>Ливандовская Анна Александровна</t>
-        </is>
-      </c>
-      <c r="E529" t="inlineStr">
-        <is>
-          <t>Утеря номерка от гардероба</t>
-        </is>
-      </c>
-      <c r="F529" s="22" t="n">
-        <v>46108</v>
-      </c>
-      <c r="G529" s="22" t="n">
-        <v>46108</v>
-      </c>
-      <c r="H529" s="22" t="n">
-        <v>46108</v>
-      </c>
-      <c r="I529" s="22" t="n">
-        <v>46108</v>
-      </c>
-      <c r="J529" t="n">
-        <v>1</v>
-      </c>
-      <c r="K529" t="n">
-        <v>0</v>
-      </c>
-      <c r="L529" t="n">
-        <v>200</v>
-      </c>
-      <c r="M529" t="n">
-        <v>200</v>
-      </c>
-      <c r="N529" t="n">
-        <v>0</v>
-      </c>
-      <c r="O529" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
-      </c>
-      <c r="P529" t="inlineStr">
-        <is>
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
     </row>
-    <row r="530" ht="15.75" customHeight="1" s="21">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>00000022030-1</t>
-        </is>
-      </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>000073471</t>
-        </is>
-      </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>+7 (921) 2291023</t>
-        </is>
-      </c>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>Гжималаускене Анна Сергеевна</t>
-        </is>
-      </c>
-      <c r="E530" t="inlineStr">
-        <is>
-          <t>Утеря номерка от гардероба</t>
-        </is>
-      </c>
-      <c r="F530" s="22" t="n">
-        <v>46125</v>
-      </c>
-      <c r="G530" s="22" t="n">
-        <v>46125</v>
-      </c>
-      <c r="H530" s="22" t="n">
-        <v>46125</v>
-      </c>
-      <c r="I530" s="22" t="n">
-        <v>46125</v>
-      </c>
-      <c r="J530" t="n">
-        <v>1</v>
-      </c>
-      <c r="K530" t="n">
-        <v>0</v>
-      </c>
-      <c r="L530" t="n">
-        <v>200</v>
-      </c>
-      <c r="M530" t="n">
-        <v>200</v>
-      </c>
-      <c r="N530" t="n">
-        <v>0</v>
-      </c>
-      <c r="O530" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
-      </c>
-      <c r="P530" t="inlineStr">
-        <is>
-          <t>Абраамян Татьяна Викторовна</t>
-        </is>
-      </c>
-    </row>
+    <row r="525" ht="15.75" customHeight="1" s="21"/>
+    <row r="526" ht="15.75" customHeight="1" s="21"/>
+    <row r="527" ht="15.75" customHeight="1" s="21"/>
+    <row r="528" ht="15.75" customHeight="1" s="21"/>
+    <row r="529" ht="15.75" customHeight="1" s="21"/>
+    <row r="530" ht="15.75" customHeight="1" s="21"/>
     <row r="531" ht="15.75" customHeight="1" s="21"/>
     <row r="532" ht="15.75" customHeight="1" s="21"/>
     <row r="533" ht="15.75" customHeight="1" s="21"/>
@@ -33286,7 +32908,7 @@
     <row r="1000" ht="15.75" customHeight="1" s="21"/>
     <row r="1001" ht="15.75" customHeight="1" s="21"/>
   </sheetData>
-  <autoFilter ref="A1:P530"/>
+  <autoFilter ref="A1:P524"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>

--- a/output/20260630_fix_owner_new_import/fitbase_import_uslugi_clientov_20260630.xlsx
+++ b/output/20260630_fix_owner_new_import/fitbase_import_uslugi_clientov_20260630.xlsx
@@ -6,7 +6,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист1'!$A$1:$P$524</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист1'!$A$1:$Q$524</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P524"/>
+  <dimension ref="A1:Q524"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12" customWidth="1" style="21" min="1" max="1"/>
@@ -434,7 +434,7 @@
     <col width="14" customWidth="1" style="21" min="14" max="14"/>
     <col width="17" customWidth="1" style="21" min="15" max="15"/>
     <col width="12" customWidth="1" style="21" min="16" max="16"/>
-    <col width="16.86" customWidth="1" style="21" min="17" max="17"/>
+    <col width="12" customWidth="1" style="21" min="17" max="17"/>
     <col width="8.710000000000001" customWidth="1" style="21" min="18" max="26"/>
   </cols>
   <sheetData>
@@ -519,6 +519,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>филиал</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -601,6 +606,11 @@
           <t xml:space="preserve">Менеджер </t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Филиал продажи</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -659,6 +669,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -720,6 +735,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -781,6 +801,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -839,6 +864,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -900,6 +930,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -961,6 +996,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1022,6 +1062,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1080,6 +1125,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1141,6 +1191,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1202,6 +1257,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1263,6 +1323,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1324,6 +1389,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1385,6 +1455,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1446,6 +1521,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1507,6 +1587,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1565,6 +1650,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1626,6 +1716,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1687,6 +1782,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1748,6 +1848,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="21">
       <c r="A22" t="inlineStr">
@@ -1809,6 +1914,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="21">
       <c r="A23" t="inlineStr">
@@ -1867,6 +1977,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="21">
       <c r="A24" t="inlineStr">
@@ -1928,6 +2043,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="21">
       <c r="A25" t="inlineStr">
@@ -1989,6 +2109,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="21">
       <c r="A26" t="inlineStr">
@@ -2047,6 +2172,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="21">
       <c r="A27" t="inlineStr">
@@ -2108,6 +2238,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="21">
       <c r="A28" t="inlineStr">
@@ -2169,6 +2304,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="21">
       <c r="A29" t="inlineStr">
@@ -2227,6 +2367,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="21">
       <c r="A30" t="inlineStr">
@@ -2288,6 +2433,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="21">
       <c r="A31" t="inlineStr">
@@ -2349,6 +2499,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="21">
       <c r="A32" t="inlineStr">
@@ -2410,6 +2565,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="21">
       <c r="A33" t="inlineStr">
@@ -2471,6 +2631,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="21">
       <c r="A34" t="inlineStr">
@@ -2529,6 +2694,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="21">
       <c r="A35" t="inlineStr">
@@ -2590,6 +2760,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="21">
       <c r="A36" t="inlineStr">
@@ -2651,6 +2826,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="21">
       <c r="A37" t="inlineStr">
@@ -2709,6 +2889,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="21">
       <c r="A38" t="inlineStr">
@@ -2767,6 +2952,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="21">
       <c r="A39" t="inlineStr">
@@ -2825,6 +3015,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="21">
       <c r="A40" t="inlineStr">
@@ -2886,6 +3081,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="21">
       <c r="A41" t="inlineStr">
@@ -2944,6 +3144,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="21">
       <c r="A42" t="inlineStr">
@@ -3005,6 +3210,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="21">
       <c r="A43" t="inlineStr">
@@ -3066,6 +3276,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="21">
       <c r="A44" t="inlineStr">
@@ -3127,6 +3342,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="21">
       <c r="A45" t="inlineStr">
@@ -3188,6 +3408,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="21">
       <c r="A46" t="inlineStr">
@@ -3246,6 +3471,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="21">
       <c r="A47" t="inlineStr">
@@ -3307,6 +3537,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="21">
       <c r="A48" t="inlineStr">
@@ -3368,6 +3603,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="21">
       <c r="A49" t="inlineStr">
@@ -3429,6 +3669,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="21">
       <c r="A50" t="inlineStr">
@@ -3487,6 +3732,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="21">
       <c r="A51" t="inlineStr">
@@ -3548,6 +3798,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="21">
       <c r="A52" t="inlineStr">
@@ -3609,6 +3864,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="21">
       <c r="A53" t="inlineStr">
@@ -3670,6 +3930,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="21">
       <c r="A54" t="inlineStr">
@@ -3728,6 +3993,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="21">
       <c r="A55" t="inlineStr">
@@ -3789,6 +4059,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="21">
       <c r="A56" t="inlineStr">
@@ -3850,6 +4125,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="21">
       <c r="A57" t="inlineStr">
@@ -3911,6 +4191,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="21">
       <c r="A58" t="inlineStr">
@@ -3969,6 +4254,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="21">
       <c r="A59" t="inlineStr">
@@ -4027,6 +4317,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="21">
       <c r="A60" t="inlineStr">
@@ -4088,6 +4383,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="21">
       <c r="A61" t="inlineStr">
@@ -4149,6 +4449,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="15.75" customHeight="1" s="21">
       <c r="A62" t="inlineStr">
@@ -4210,6 +4515,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="21">
       <c r="A63" t="inlineStr">
@@ -4268,6 +4578,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="15.75" customHeight="1" s="21">
       <c r="A64" t="inlineStr">
@@ -4329,6 +4644,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="21">
       <c r="A65" t="inlineStr">
@@ -4387,6 +4707,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="21">
       <c r="A66" t="inlineStr">
@@ -4448,6 +4773,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="21">
       <c r="A67" t="inlineStr">
@@ -4509,6 +4839,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="21">
       <c r="A68" t="inlineStr">
@@ -4567,6 +4902,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="21">
       <c r="A69" t="inlineStr">
@@ -4625,6 +4965,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="21">
       <c r="A70" t="inlineStr">
@@ -4683,6 +5028,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="21">
       <c r="A71" t="inlineStr">
@@ -4744,6 +5094,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="15.75" customHeight="1" s="21">
       <c r="A72" t="inlineStr">
@@ -4805,6 +5160,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="15.75" customHeight="1" s="21">
       <c r="A73" t="inlineStr">
@@ -4866,6 +5226,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="21">
       <c r="A74" t="inlineStr">
@@ -4924,6 +5289,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="15.75" customHeight="1" s="21">
       <c r="A75" t="inlineStr">
@@ -4982,6 +5352,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="15.75" customHeight="1" s="21">
       <c r="A76" t="inlineStr">
@@ -5040,6 +5415,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="15.75" customHeight="1" s="21">
       <c r="A77" t="inlineStr">
@@ -5101,6 +5481,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="15.75" customHeight="1" s="21">
       <c r="A78" t="inlineStr">
@@ -5162,6 +5547,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="15.75" customHeight="1" s="21">
       <c r="A79" t="inlineStr">
@@ -5220,6 +5610,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="15.75" customHeight="1" s="21">
       <c r="A80" t="inlineStr">
@@ -5278,6 +5673,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="15.75" customHeight="1" s="21">
       <c r="A81" t="inlineStr">
@@ -5339,6 +5739,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="15.75" customHeight="1" s="21">
       <c r="A82" t="inlineStr">
@@ -5400,6 +5805,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="15.75" customHeight="1" s="21">
       <c r="A83" t="inlineStr">
@@ -5461,6 +5871,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="15.75" customHeight="1" s="21">
       <c r="A84" t="inlineStr">
@@ -5522,6 +5937,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="15.75" customHeight="1" s="21">
       <c r="A85" t="inlineStr">
@@ -5580,6 +6000,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="15.75" customHeight="1" s="21">
       <c r="A86" t="inlineStr">
@@ -5641,6 +6066,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="15.75" customHeight="1" s="21">
       <c r="A87" t="inlineStr">
@@ -5702,6 +6132,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="15.75" customHeight="1" s="21">
       <c r="A88" t="inlineStr">
@@ -5760,6 +6195,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="15.75" customHeight="1" s="21">
       <c r="A89" t="inlineStr">
@@ -5821,6 +6261,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="15.75" customHeight="1" s="21">
       <c r="A90" t="inlineStr">
@@ -5882,6 +6327,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="15.75" customHeight="1" s="21">
       <c r="A91" t="inlineStr">
@@ -5943,6 +6393,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="15.75" customHeight="1" s="21">
       <c r="A92" t="inlineStr">
@@ -6004,6 +6459,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="15.75" customHeight="1" s="21">
       <c r="A93" t="inlineStr">
@@ -6065,6 +6525,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="15.75" customHeight="1" s="21">
       <c r="A94" t="inlineStr">
@@ -6126,6 +6591,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="15.75" customHeight="1" s="21">
       <c r="A95" t="inlineStr">
@@ -6187,6 +6657,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="15.75" customHeight="1" s="21">
       <c r="A96" t="inlineStr">
@@ -6248,6 +6723,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="15.75" customHeight="1" s="21">
       <c r="A97" t="inlineStr">
@@ -6306,6 +6786,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="15.75" customHeight="1" s="21">
       <c r="A98" t="inlineStr">
@@ -6364,6 +6849,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="15.75" customHeight="1" s="21">
       <c r="A99" t="inlineStr">
@@ -6425,6 +6915,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="15.75" customHeight="1" s="21">
       <c r="A100" t="inlineStr">
@@ -6483,6 +6978,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="15.75" customHeight="1" s="21">
       <c r="A101" t="inlineStr">
@@ -6544,6 +7044,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="15.75" customHeight="1" s="21">
       <c r="A102" t="inlineStr">
@@ -6605,6 +7110,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="15.75" customHeight="1" s="21">
       <c r="A103" t="inlineStr">
@@ -6666,6 +7176,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="15.75" customHeight="1" s="21">
       <c r="A104" t="inlineStr">
@@ -6727,6 +7242,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="15.75" customHeight="1" s="21">
       <c r="A105" t="inlineStr">
@@ -6785,6 +7305,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="15.75" customHeight="1" s="21">
       <c r="A106" t="inlineStr">
@@ -6843,6 +7368,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="15.75" customHeight="1" s="21">
       <c r="A107" t="inlineStr">
@@ -6904,6 +7434,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="15.75" customHeight="1" s="21">
       <c r="A108" t="inlineStr">
@@ -6962,6 +7497,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="15.75" customHeight="1" s="21">
       <c r="A109" t="inlineStr">
@@ -7023,6 +7563,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="15.75" customHeight="1" s="21">
       <c r="A110" t="inlineStr">
@@ -7084,6 +7629,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="15.75" customHeight="1" s="21">
       <c r="A111" t="inlineStr">
@@ -7145,6 +7695,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="15.75" customHeight="1" s="21">
       <c r="A112" t="inlineStr">
@@ -7203,6 +7758,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="15.75" customHeight="1" s="21">
       <c r="A113" t="inlineStr">
@@ -7261,6 +7821,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="15.75" customHeight="1" s="21">
       <c r="A114" t="inlineStr">
@@ -7322,6 +7887,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="15.75" customHeight="1" s="21">
       <c r="A115" t="inlineStr">
@@ -7380,6 +7950,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15.75" customHeight="1" s="21">
       <c r="A116" t="inlineStr">
@@ -7438,6 +8013,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="15.75" customHeight="1" s="21">
       <c r="A117" t="inlineStr">
@@ -7496,6 +8076,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="15.75" customHeight="1" s="21">
       <c r="A118" t="inlineStr">
@@ -7557,6 +8142,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="15.75" customHeight="1" s="21">
       <c r="A119" t="inlineStr">
@@ -7615,6 +8205,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="15.75" customHeight="1" s="21">
       <c r="A120" t="inlineStr">
@@ -7676,6 +8271,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="15.75" customHeight="1" s="21">
       <c r="A121" t="inlineStr">
@@ -7734,6 +8334,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="15.75" customHeight="1" s="21">
       <c r="A122" t="inlineStr">
@@ -7795,6 +8400,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="15.75" customHeight="1" s="21">
       <c r="A123" t="inlineStr">
@@ -7856,6 +8466,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="15.75" customHeight="1" s="21">
       <c r="A124" t="inlineStr">
@@ -7917,6 +8532,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="15.75" customHeight="1" s="21">
       <c r="A125" t="inlineStr">
@@ -7978,6 +8598,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="15.75" customHeight="1" s="21">
       <c r="A126" t="inlineStr">
@@ -8039,6 +8664,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="15.75" customHeight="1" s="21">
       <c r="A127" t="inlineStr">
@@ -8100,6 +8730,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="15.75" customHeight="1" s="21">
       <c r="A128" t="inlineStr">
@@ -8158,6 +8793,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="15.75" customHeight="1" s="21">
       <c r="A129" t="inlineStr">
@@ -8219,6 +8859,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="15.75" customHeight="1" s="21">
       <c r="A130" t="inlineStr">
@@ -8277,6 +8922,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="15.75" customHeight="1" s="21">
       <c r="A131" t="inlineStr">
@@ -8338,6 +8988,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="15.75" customHeight="1" s="21">
       <c r="A132" t="inlineStr">
@@ -8399,6 +9054,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="15.75" customHeight="1" s="21">
       <c r="A133" t="inlineStr">
@@ -8460,6 +9120,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="15.75" customHeight="1" s="21">
       <c r="A134" t="inlineStr">
@@ -8521,6 +9186,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="15.75" customHeight="1" s="21">
       <c r="A135" t="inlineStr">
@@ -8582,6 +9252,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="15.75" customHeight="1" s="21">
       <c r="A136" t="inlineStr">
@@ -8643,6 +9318,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="15.75" customHeight="1" s="21">
       <c r="A137" t="inlineStr">
@@ -8701,6 +9381,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="15.75" customHeight="1" s="21">
       <c r="A138" t="inlineStr">
@@ -8759,6 +9444,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="15.75" customHeight="1" s="21">
       <c r="A139" t="inlineStr">
@@ -8817,6 +9507,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="15.75" customHeight="1" s="21">
       <c r="A140" t="inlineStr">
@@ -8875,6 +9570,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="15.75" customHeight="1" s="21">
       <c r="A141" t="inlineStr">
@@ -8933,6 +9633,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="15.75" customHeight="1" s="21">
       <c r="A142" t="inlineStr">
@@ -8991,6 +9696,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="15.75" customHeight="1" s="21">
       <c r="A143" t="inlineStr">
@@ -9052,6 +9762,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="15.75" customHeight="1" s="21">
       <c r="A144" t="inlineStr">
@@ -9110,6 +9825,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="15.75" customHeight="1" s="21">
       <c r="A145" t="inlineStr">
@@ -9168,6 +9888,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="15.75" customHeight="1" s="21">
       <c r="A146" t="inlineStr">
@@ -9226,6 +9951,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="15.75" customHeight="1" s="21">
       <c r="A147" t="inlineStr">
@@ -9284,6 +10014,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="15.75" customHeight="1" s="21">
       <c r="A148" t="inlineStr">
@@ -9345,6 +10080,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="15.75" customHeight="1" s="21">
       <c r="A149" t="inlineStr">
@@ -9406,6 +10146,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="15.75" customHeight="1" s="21">
       <c r="A150" t="inlineStr">
@@ -9463,6 +10208,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="15.75" customHeight="1" s="21">
       <c r="A151" t="inlineStr">
@@ -9524,6 +10274,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="15.75" customHeight="1" s="21">
       <c r="A152" t="inlineStr">
@@ -9585,6 +10340,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="15.75" customHeight="1" s="21">
       <c r="A153" t="inlineStr">
@@ -9643,6 +10403,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="15.75" customHeight="1" s="21">
       <c r="A154" t="inlineStr">
@@ -9701,6 +10466,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="15.75" customHeight="1" s="21">
       <c r="A155" t="inlineStr">
@@ -9762,6 +10532,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="15.75" customHeight="1" s="21">
       <c r="A156" t="inlineStr">
@@ -9823,6 +10598,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="15.75" customHeight="1" s="21">
       <c r="A157" t="inlineStr">
@@ -9881,6 +10661,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="15.75" customHeight="1" s="21">
       <c r="A158" t="inlineStr">
@@ -9939,6 +10724,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="15.75" customHeight="1" s="21">
       <c r="A159" t="inlineStr">
@@ -9997,6 +10787,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="15.75" customHeight="1" s="21">
       <c r="A160" t="inlineStr">
@@ -10055,6 +10850,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="15.75" customHeight="1" s="21">
       <c r="A161" t="inlineStr">
@@ -10116,6 +10916,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="15.75" customHeight="1" s="21">
       <c r="A162" t="inlineStr">
@@ -10174,6 +10979,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="15.75" customHeight="1" s="21">
       <c r="A163" t="inlineStr">
@@ -10232,6 +11042,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="15.75" customHeight="1" s="21">
       <c r="A164" t="inlineStr">
@@ -10293,6 +11108,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="15.75" customHeight="1" s="21">
       <c r="A165" t="inlineStr">
@@ -10351,6 +11171,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="15.75" customHeight="1" s="21">
       <c r="A166" t="inlineStr">
@@ -10412,6 +11237,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="15.75" customHeight="1" s="21">
       <c r="A167" t="inlineStr">
@@ -10473,6 +11303,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="15.75" customHeight="1" s="21">
       <c r="A168" t="inlineStr">
@@ -10531,6 +11366,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="15.75" customHeight="1" s="21">
       <c r="A169" t="inlineStr">
@@ -10589,6 +11429,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="15.75" customHeight="1" s="21">
       <c r="A170" t="inlineStr">
@@ -10647,6 +11492,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="15.75" customHeight="1" s="21">
       <c r="A171" t="inlineStr">
@@ -10708,6 +11558,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="15.75" customHeight="1" s="21">
       <c r="A172" t="inlineStr">
@@ -10769,6 +11624,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="15.75" customHeight="1" s="21">
       <c r="A173" t="inlineStr">
@@ -10827,6 +11687,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="15.75" customHeight="1" s="21">
       <c r="A174" t="inlineStr">
@@ -10888,6 +11753,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="15.75" customHeight="1" s="21">
       <c r="A175" t="inlineStr">
@@ -10949,6 +11819,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="15.75" customHeight="1" s="21">
       <c r="A176" t="inlineStr">
@@ -11010,6 +11885,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="15.75" customHeight="1" s="21">
       <c r="A177" t="inlineStr">
@@ -11068,6 +11948,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="15.75" customHeight="1" s="21">
       <c r="A178" t="inlineStr">
@@ -11129,6 +12014,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="15.75" customHeight="1" s="21">
       <c r="A179" t="inlineStr">
@@ -11187,6 +12077,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="15.75" customHeight="1" s="21">
       <c r="A180" t="inlineStr">
@@ -11248,6 +12143,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="15.75" customHeight="1" s="21">
       <c r="A181" t="inlineStr">
@@ -11309,6 +12209,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="15.75" customHeight="1" s="21">
       <c r="A182" t="inlineStr">
@@ -11370,6 +12275,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="15.75" customHeight="1" s="21">
       <c r="A183" t="inlineStr">
@@ -11431,6 +12341,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="15.75" customHeight="1" s="21">
       <c r="A184" t="inlineStr">
@@ -11489,6 +12404,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="15.75" customHeight="1" s="21">
       <c r="A185" t="inlineStr">
@@ -11550,6 +12470,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="15.75" customHeight="1" s="21">
       <c r="A186" t="inlineStr">
@@ -11611,6 +12536,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="15.75" customHeight="1" s="21">
       <c r="A187" t="inlineStr">
@@ -11672,6 +12602,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="15.75" customHeight="1" s="21">
       <c r="A188" t="inlineStr">
@@ -11733,6 +12668,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="15.75" customHeight="1" s="21">
       <c r="A189" t="inlineStr">
@@ -11794,6 +12734,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="15.75" customHeight="1" s="21">
       <c r="A190" t="inlineStr">
@@ -11855,6 +12800,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="15.75" customHeight="1" s="21">
       <c r="A191" t="inlineStr">
@@ -11912,6 +12862,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="15.75" customHeight="1" s="21">
       <c r="A192" t="inlineStr">
@@ -11970,6 +12925,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="15.75" customHeight="1" s="21">
       <c r="A193" t="inlineStr">
@@ -12031,6 +12991,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="15.75" customHeight="1" s="21">
       <c r="A194" t="inlineStr">
@@ -12089,6 +13054,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="15.75" customHeight="1" s="21">
       <c r="A195" t="inlineStr">
@@ -12150,6 +13120,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="15.75" customHeight="1" s="21">
       <c r="A196" t="inlineStr">
@@ -12211,6 +13186,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="15.75" customHeight="1" s="21">
       <c r="A197" t="inlineStr">
@@ -12272,6 +13252,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="15.75" customHeight="1" s="21">
       <c r="A198" t="inlineStr">
@@ -12333,6 +13318,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="15.75" customHeight="1" s="21">
       <c r="A199" t="inlineStr">
@@ -12394,6 +13384,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="15.75" customHeight="1" s="21">
       <c r="A200" t="inlineStr">
@@ -12455,6 +13450,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="15.75" customHeight="1" s="21">
       <c r="A201" t="inlineStr">
@@ -12516,6 +13516,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="15.75" customHeight="1" s="21">
       <c r="A202" t="inlineStr">
@@ -12577,6 +13582,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="15.75" customHeight="1" s="21">
       <c r="A203" t="inlineStr">
@@ -12638,6 +13648,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="15.75" customHeight="1" s="21">
       <c r="A204" t="inlineStr">
@@ -12699,6 +13714,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="15.75" customHeight="1" s="21">
       <c r="A205" t="inlineStr">
@@ -12760,6 +13780,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="15.75" customHeight="1" s="21">
       <c r="A206" t="inlineStr">
@@ -12821,6 +13846,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="15.75" customHeight="1" s="21">
       <c r="A207" t="inlineStr">
@@ -12879,6 +13909,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="15.75" customHeight="1" s="21">
       <c r="A208" t="inlineStr">
@@ -12937,6 +13972,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="15.75" customHeight="1" s="21">
       <c r="A209" t="inlineStr">
@@ -12998,6 +14038,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="15.75" customHeight="1" s="21">
       <c r="A210" t="inlineStr">
@@ -13056,6 +14101,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="15.75" customHeight="1" s="21">
       <c r="A211" t="inlineStr">
@@ -13114,6 +14164,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="15.75" customHeight="1" s="21">
       <c r="A212" t="inlineStr">
@@ -13172,6 +14227,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="15.75" customHeight="1" s="21">
       <c r="A213" t="inlineStr">
@@ -13233,6 +14293,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="15.75" customHeight="1" s="21">
       <c r="A214" t="inlineStr">
@@ -13294,6 +14359,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="15.75" customHeight="1" s="21">
       <c r="A215" t="inlineStr">
@@ -13355,6 +14425,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="15.75" customHeight="1" s="21">
       <c r="A216" t="inlineStr">
@@ -13416,6 +14491,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="15.75" customHeight="1" s="21">
       <c r="A217" t="inlineStr">
@@ -13477,6 +14557,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="15.75" customHeight="1" s="21">
       <c r="A218" t="inlineStr">
@@ -13535,6 +14620,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="15.75" customHeight="1" s="21">
       <c r="A219" t="inlineStr">
@@ -13596,6 +14686,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="15.75" customHeight="1" s="21">
       <c r="A220" t="inlineStr">
@@ -13657,6 +14752,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="15.75" customHeight="1" s="21">
       <c r="A221" t="inlineStr">
@@ -13718,6 +14818,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="15.75" customHeight="1" s="21">
       <c r="A222" t="inlineStr">
@@ -13779,6 +14884,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="15.75" customHeight="1" s="21">
       <c r="A223" t="inlineStr">
@@ -13840,6 +14950,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="15.75" customHeight="1" s="21">
       <c r="A224" t="inlineStr">
@@ -13901,6 +15016,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="15.75" customHeight="1" s="21">
       <c r="A225" t="inlineStr">
@@ -13962,6 +15082,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="15.75" customHeight="1" s="21">
       <c r="A226" t="inlineStr">
@@ -14020,6 +15145,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="15.75" customHeight="1" s="21">
       <c r="A227" t="inlineStr">
@@ -14078,6 +15208,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="15.75" customHeight="1" s="21">
       <c r="A228" t="inlineStr">
@@ -14136,6 +15271,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="15.75" customHeight="1" s="21">
       <c r="A229" t="inlineStr">
@@ -14194,6 +15334,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="15.75" customHeight="1" s="21">
       <c r="A230" t="inlineStr">
@@ -14252,6 +15397,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="15.75" customHeight="1" s="21">
       <c r="A231" t="inlineStr">
@@ -14310,6 +15460,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="15.75" customHeight="1" s="21">
       <c r="A232" t="inlineStr">
@@ -14368,6 +15523,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="15.75" customHeight="1" s="21">
       <c r="A233" t="inlineStr">
@@ -14429,6 +15589,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="15.75" customHeight="1" s="21">
       <c r="A234" t="inlineStr">
@@ -14490,6 +15655,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="15.75" customHeight="1" s="21">
       <c r="A235" t="inlineStr">
@@ -14548,6 +15718,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="15.75" customHeight="1" s="21">
       <c r="A236" t="inlineStr">
@@ -14609,6 +15784,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="15.75" customHeight="1" s="21">
       <c r="A237" t="inlineStr">
@@ -14670,6 +15850,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="15.75" customHeight="1" s="21">
       <c r="A238" t="inlineStr">
@@ -14728,6 +15913,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="15.75" customHeight="1" s="21">
       <c r="A239" t="inlineStr">
@@ -14789,6 +15979,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="15.75" customHeight="1" s="21">
       <c r="A240" t="inlineStr">
@@ -14847,6 +16042,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="15.75" customHeight="1" s="21">
       <c r="A241" t="inlineStr">
@@ -14905,6 +16105,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="15.75" customHeight="1" s="21">
       <c r="A242" t="inlineStr">
@@ -14963,6 +16168,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="15.75" customHeight="1" s="21">
       <c r="A243" t="inlineStr">
@@ -15021,6 +16231,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="15.75" customHeight="1" s="21">
       <c r="A244" t="inlineStr">
@@ -15079,6 +16294,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="15.75" customHeight="1" s="21">
       <c r="A245" t="inlineStr">
@@ -15140,6 +16360,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="15.75" customHeight="1" s="21">
       <c r="A246" t="inlineStr">
@@ -15198,6 +16423,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="15.75" customHeight="1" s="21">
       <c r="A247" t="inlineStr">
@@ -15256,6 +16486,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="15.75" customHeight="1" s="21">
       <c r="A248" t="inlineStr">
@@ -15314,6 +16549,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="15.75" customHeight="1" s="21">
       <c r="A249" t="inlineStr">
@@ -15372,6 +16612,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="15.75" customHeight="1" s="21">
       <c r="A250" t="inlineStr">
@@ -15430,6 +16675,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="15.75" customHeight="1" s="21">
       <c r="A251" t="inlineStr">
@@ -15488,6 +16738,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="15.75" customHeight="1" s="21">
       <c r="A252" t="inlineStr">
@@ -15546,6 +16801,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="15.75" customHeight="1" s="21">
       <c r="A253" t="inlineStr">
@@ -15604,6 +16864,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="15.75" customHeight="1" s="21">
       <c r="A254" t="inlineStr">
@@ -15662,6 +16927,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="15.75" customHeight="1" s="21">
       <c r="A255" t="inlineStr">
@@ -15720,6 +16990,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="15.75" customHeight="1" s="21">
       <c r="A256" t="inlineStr">
@@ -15778,6 +17053,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="15.75" customHeight="1" s="21">
       <c r="A257" t="inlineStr">
@@ -15836,6 +17116,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="15.75" customHeight="1" s="21">
       <c r="A258" t="inlineStr">
@@ -15894,6 +17179,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="15.75" customHeight="1" s="21">
       <c r="A259" t="inlineStr">
@@ -15952,6 +17242,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="15.75" customHeight="1" s="21">
       <c r="A260" t="inlineStr">
@@ -16010,6 +17305,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="15.75" customHeight="1" s="21">
       <c r="A261" t="inlineStr">
@@ -16068,6 +17368,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="15.75" customHeight="1" s="21">
       <c r="A262" t="inlineStr">
@@ -16126,6 +17431,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="15.75" customHeight="1" s="21">
       <c r="A263" t="inlineStr">
@@ -16184,6 +17494,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="15.75" customHeight="1" s="21">
       <c r="A264" t="inlineStr">
@@ -16242,6 +17557,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="15.75" customHeight="1" s="21">
       <c r="A265" t="inlineStr">
@@ -16300,6 +17620,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="15.75" customHeight="1" s="21">
       <c r="A266" t="inlineStr">
@@ -16358,6 +17683,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="15.75" customHeight="1" s="21">
       <c r="A267" t="inlineStr">
@@ -16416,6 +17746,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="15.75" customHeight="1" s="21">
       <c r="A268" t="inlineStr">
@@ -16474,6 +17809,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="15.75" customHeight="1" s="21">
       <c r="A269" t="inlineStr">
@@ -16532,6 +17872,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="15.75" customHeight="1" s="21">
       <c r="A270" t="inlineStr">
@@ -16590,6 +17935,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="15.75" customHeight="1" s="21">
       <c r="A271" t="inlineStr">
@@ -16648,6 +17998,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="15.75" customHeight="1" s="21">
       <c r="A272" t="inlineStr">
@@ -16706,6 +18061,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="15.75" customHeight="1" s="21">
       <c r="A273" t="inlineStr">
@@ -16764,6 +18124,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="15.75" customHeight="1" s="21">
       <c r="A274" t="inlineStr">
@@ -16822,6 +18187,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="15.75" customHeight="1" s="21">
       <c r="A275" t="inlineStr">
@@ -16883,6 +18253,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="15.75" customHeight="1" s="21">
       <c r="A276" t="inlineStr">
@@ -16944,6 +18319,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="15.75" customHeight="1" s="21">
       <c r="A277" t="inlineStr">
@@ -17005,6 +18385,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="15.75" customHeight="1" s="21">
       <c r="A278" t="inlineStr">
@@ -17063,6 +18448,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="15.75" customHeight="1" s="21">
       <c r="A279" t="inlineStr">
@@ -17121,6 +18511,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="15.75" customHeight="1" s="21">
       <c r="A280" t="inlineStr">
@@ -17179,6 +18574,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="15.75" customHeight="1" s="21">
       <c r="A281" t="inlineStr">
@@ -17237,6 +18637,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="15.75" customHeight="1" s="21">
       <c r="A282" t="inlineStr">
@@ -17298,6 +18703,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="15.75" customHeight="1" s="21">
       <c r="A283" t="inlineStr">
@@ -17356,6 +18766,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="15.75" customHeight="1" s="21">
       <c r="A284" t="inlineStr">
@@ -17414,6 +18829,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="15.75" customHeight="1" s="21">
       <c r="A285" t="inlineStr">
@@ -17472,6 +18892,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="15.75" customHeight="1" s="21">
       <c r="A286" t="inlineStr">
@@ -17533,6 +18958,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="15.75" customHeight="1" s="21">
       <c r="A287" t="inlineStr">
@@ -17591,6 +19021,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="15.75" customHeight="1" s="21">
       <c r="A288" t="inlineStr">
@@ -17649,6 +19084,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="15.75" customHeight="1" s="21">
       <c r="A289" t="inlineStr">
@@ -17710,6 +19150,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="290" ht="15.75" customHeight="1" s="21">
       <c r="A290" t="inlineStr">
@@ -17771,6 +19216,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="291" ht="15.75" customHeight="1" s="21">
       <c r="A291" t="inlineStr">
@@ -17832,6 +19282,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="15.75" customHeight="1" s="21">
       <c r="A292" t="inlineStr">
@@ -17890,6 +19345,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="15.75" customHeight="1" s="21">
       <c r="A293" t="inlineStr">
@@ -17948,6 +19408,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="15.75" customHeight="1" s="21">
       <c r="A294" t="inlineStr">
@@ -18009,6 +19474,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="295" ht="15.75" customHeight="1" s="21">
       <c r="A295" t="inlineStr">
@@ -18070,6 +19540,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="15.75" customHeight="1" s="21">
       <c r="A296" t="inlineStr">
@@ -18131,6 +19606,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="15.75" customHeight="1" s="21">
       <c r="A297" t="inlineStr">
@@ -18192,6 +19672,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="15.75" customHeight="1" s="21">
       <c r="A298" t="inlineStr">
@@ -18250,6 +19735,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="299" ht="15.75" customHeight="1" s="21">
       <c r="A299" t="inlineStr">
@@ -18311,6 +19801,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="15.75" customHeight="1" s="21">
       <c r="A300" t="inlineStr">
@@ -18372,6 +19867,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="15.75" customHeight="1" s="21">
       <c r="A301" t="inlineStr">
@@ -18433,6 +19933,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="15.75" customHeight="1" s="21">
       <c r="A302" t="inlineStr">
@@ -18494,6 +19999,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="15.75" customHeight="1" s="21">
       <c r="A303" t="inlineStr">
@@ -18552,6 +20062,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="15.75" customHeight="1" s="21">
       <c r="A304" t="inlineStr">
@@ -18613,6 +20128,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="305" ht="15.75" customHeight="1" s="21">
       <c r="A305" t="inlineStr">
@@ -18674,6 +20194,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="15.75" customHeight="1" s="21">
       <c r="A306" t="inlineStr">
@@ -18732,6 +20257,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="15.75" customHeight="1" s="21">
       <c r="A307" t="inlineStr">
@@ -18790,6 +20320,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="308" ht="15.75" customHeight="1" s="21">
       <c r="A308" t="inlineStr">
@@ -18851,6 +20386,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="309" ht="15.75" customHeight="1" s="21">
       <c r="A309" t="inlineStr">
@@ -18912,6 +20452,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="310" ht="15.75" customHeight="1" s="21">
       <c r="A310" t="inlineStr">
@@ -18970,6 +20515,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="15.75" customHeight="1" s="21">
       <c r="A311" t="inlineStr">
@@ -19031,6 +20581,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="15.75" customHeight="1" s="21">
       <c r="A312" t="inlineStr">
@@ -19089,6 +20644,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="313" ht="15.75" customHeight="1" s="21">
       <c r="A313" t="inlineStr">
@@ -19150,6 +20710,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="314" ht="15.75" customHeight="1" s="21">
       <c r="A314" t="inlineStr">
@@ -19211,6 +20776,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="315" ht="15.75" customHeight="1" s="21">
       <c r="A315" t="inlineStr">
@@ -19272,6 +20842,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="316" ht="15.75" customHeight="1" s="21">
       <c r="A316" t="inlineStr">
@@ -19330,6 +20905,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="317" ht="15.75" customHeight="1" s="21">
       <c r="A317" t="inlineStr">
@@ -19391,6 +20971,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="318" ht="15.75" customHeight="1" s="21">
       <c r="A318" t="inlineStr">
@@ -19452,6 +21037,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="319" ht="15.75" customHeight="1" s="21">
       <c r="A319" t="inlineStr">
@@ -19510,6 +21100,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="320" ht="15.75" customHeight="1" s="21">
       <c r="A320" t="inlineStr">
@@ -19568,6 +21163,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="321" ht="15.75" customHeight="1" s="21">
       <c r="A321" t="inlineStr">
@@ -19629,6 +21229,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="322" ht="15.75" customHeight="1" s="21">
       <c r="A322" t="inlineStr">
@@ -19690,6 +21295,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="323" ht="15.75" customHeight="1" s="21">
       <c r="A323" t="inlineStr">
@@ -19748,6 +21358,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="324" ht="15.75" customHeight="1" s="21">
       <c r="A324" t="inlineStr">
@@ -19809,6 +21424,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="325" ht="15.75" customHeight="1" s="21">
       <c r="A325" t="inlineStr">
@@ -19867,6 +21487,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="326" ht="15.75" customHeight="1" s="21">
       <c r="A326" t="inlineStr">
@@ -19928,6 +21553,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="327" ht="15.75" customHeight="1" s="21">
       <c r="A327" t="inlineStr">
@@ -19989,6 +21619,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="328" ht="15.75" customHeight="1" s="21">
       <c r="A328" t="inlineStr">
@@ -20050,6 +21685,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="329" ht="15.75" customHeight="1" s="21">
       <c r="A329" t="inlineStr">
@@ -20111,6 +21751,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="330" ht="15.75" customHeight="1" s="21">
       <c r="A330" t="inlineStr">
@@ -20169,6 +21814,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="331" ht="15.75" customHeight="1" s="21">
       <c r="A331" t="inlineStr">
@@ -20230,6 +21880,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="332" ht="15.75" customHeight="1" s="21">
       <c r="A332" t="inlineStr">
@@ -20288,6 +21943,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="333" ht="15.75" customHeight="1" s="21">
       <c r="A333" t="inlineStr">
@@ -20349,6 +22009,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="334" ht="15.75" customHeight="1" s="21">
       <c r="A334" t="inlineStr">
@@ -20407,6 +22072,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="335" ht="15.75" customHeight="1" s="21">
       <c r="A335" t="inlineStr">
@@ -20465,6 +22135,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="336" ht="15.75" customHeight="1" s="21">
       <c r="A336" t="inlineStr">
@@ -20526,6 +22201,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="337" ht="15.75" customHeight="1" s="21">
       <c r="A337" t="inlineStr">
@@ -20584,6 +22264,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="338" ht="15.75" customHeight="1" s="21">
       <c r="A338" t="inlineStr">
@@ -20645,6 +22330,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="339" ht="15.75" customHeight="1" s="21">
       <c r="A339" t="inlineStr">
@@ -20706,6 +22396,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="340" ht="15.75" customHeight="1" s="21">
       <c r="A340" t="inlineStr">
@@ -20767,6 +22462,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="341" ht="15.75" customHeight="1" s="21">
       <c r="A341" t="inlineStr">
@@ -20828,6 +22528,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="342" ht="15.75" customHeight="1" s="21">
       <c r="A342" t="inlineStr">
@@ -20886,6 +22591,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="343" ht="15.75" customHeight="1" s="21">
       <c r="A343" t="inlineStr">
@@ -20944,6 +22654,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="344" ht="15.75" customHeight="1" s="21">
       <c r="A344" t="inlineStr">
@@ -21002,6 +22717,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="345" ht="15.75" customHeight="1" s="21">
       <c r="A345" t="inlineStr">
@@ -21060,6 +22780,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="346" ht="15.75" customHeight="1" s="21">
       <c r="A346" t="inlineStr">
@@ -21118,6 +22843,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="347" ht="15.75" customHeight="1" s="21">
       <c r="A347" t="inlineStr">
@@ -21176,6 +22906,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="348" ht="15.75" customHeight="1" s="21">
       <c r="A348" t="inlineStr">
@@ -21234,6 +22969,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="349" ht="15.75" customHeight="1" s="21">
       <c r="A349" t="inlineStr">
@@ -21292,6 +23032,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="350" ht="15.75" customHeight="1" s="21">
       <c r="A350" t="inlineStr">
@@ -21350,6 +23095,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="351" ht="15.75" customHeight="1" s="21">
       <c r="A351" t="inlineStr">
@@ -21408,6 +23158,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="352" ht="15.75" customHeight="1" s="21">
       <c r="A352" t="inlineStr">
@@ -21466,6 +23221,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="353" ht="15.75" customHeight="1" s="21">
       <c r="A353" t="inlineStr">
@@ -21524,6 +23284,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="354" ht="15.75" customHeight="1" s="21">
       <c r="A354" t="inlineStr">
@@ -21582,6 +23347,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="355" ht="15.75" customHeight="1" s="21">
       <c r="A355" t="inlineStr">
@@ -21646,6 +23416,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="356" ht="15.75" customHeight="1" s="21">
       <c r="A356" t="inlineStr">
@@ -21710,6 +23485,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="357" ht="15.75" customHeight="1" s="21">
       <c r="A357" t="inlineStr">
@@ -21774,6 +23554,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="358" ht="15.75" customHeight="1" s="21">
       <c r="A358" t="inlineStr">
@@ -21838,6 +23623,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="359" ht="15.75" customHeight="1" s="21">
       <c r="A359" t="inlineStr">
@@ -21902,6 +23692,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="360" ht="15.75" customHeight="1" s="21">
       <c r="A360" t="inlineStr">
@@ -21966,6 +23761,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="361" ht="15.75" customHeight="1" s="21">
       <c r="A361" t="inlineStr">
@@ -22030,6 +23830,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="362" ht="15.75" customHeight="1" s="21">
       <c r="A362" t="inlineStr">
@@ -22094,6 +23899,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="363" ht="15.75" customHeight="1" s="21">
       <c r="A363" t="inlineStr">
@@ -22158,6 +23968,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="364" ht="15.75" customHeight="1" s="21">
       <c r="A364" t="inlineStr">
@@ -22222,6 +24037,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="365" ht="15.75" customHeight="1" s="21">
       <c r="A365" t="inlineStr">
@@ -22286,6 +24106,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="366" ht="15.75" customHeight="1" s="21">
       <c r="A366" t="inlineStr">
@@ -22350,6 +24175,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="367" ht="15.75" customHeight="1" s="21">
       <c r="A367" t="inlineStr">
@@ -22414,6 +24244,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="368" ht="15.75" customHeight="1" s="21">
       <c r="A368" t="inlineStr">
@@ -22478,6 +24313,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="369" ht="15.75" customHeight="1" s="21">
       <c r="A369" t="inlineStr">
@@ -22542,6 +24382,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="370" ht="15.75" customHeight="1" s="21">
       <c r="A370" t="inlineStr">
@@ -22606,6 +24451,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="371" ht="15.75" customHeight="1" s="21">
       <c r="A371" t="inlineStr">
@@ -22670,6 +24520,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="372" ht="15.75" customHeight="1" s="21">
       <c r="A372" t="inlineStr">
@@ -22734,6 +24589,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="373" ht="15.75" customHeight="1" s="21">
       <c r="A373" t="inlineStr">
@@ -22798,6 +24658,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="374" ht="15.75" customHeight="1" s="21">
       <c r="A374" t="inlineStr">
@@ -22862,6 +24727,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="375" ht="15.75" customHeight="1" s="21">
       <c r="A375" t="inlineStr">
@@ -22926,6 +24796,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="376" ht="15.75" customHeight="1" s="21">
       <c r="A376" t="inlineStr">
@@ -22990,6 +24865,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="377" ht="15.75" customHeight="1" s="21">
       <c r="A377" t="inlineStr">
@@ -23054,6 +24934,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="378" ht="15.75" customHeight="1" s="21">
       <c r="A378" t="inlineStr">
@@ -23118,6 +25003,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="379" ht="15.75" customHeight="1" s="21">
       <c r="A379" t="inlineStr">
@@ -23182,6 +25072,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="380" ht="15.75" customHeight="1" s="21">
       <c r="A380" t="inlineStr">
@@ -23246,6 +25141,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="381" ht="15.75" customHeight="1" s="21">
       <c r="A381" t="inlineStr">
@@ -23310,6 +25210,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="382" ht="15.75" customHeight="1" s="21">
       <c r="A382" t="inlineStr">
@@ -23374,6 +25279,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="383" ht="15.75" customHeight="1" s="21">
       <c r="A383" t="inlineStr">
@@ -23438,6 +25348,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="384" ht="15.75" customHeight="1" s="21">
       <c r="A384" t="inlineStr">
@@ -23502,6 +25417,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="385" ht="15.75" customHeight="1" s="21">
       <c r="A385" t="inlineStr">
@@ -23566,6 +25486,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="386" ht="15.75" customHeight="1" s="21">
       <c r="A386" t="inlineStr">
@@ -23626,6 +25551,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="387" ht="15.75" customHeight="1" s="21">
       <c r="A387" t="inlineStr">
@@ -23686,6 +25616,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="388" ht="15.75" customHeight="1" s="21">
       <c r="A388" t="inlineStr">
@@ -23746,6 +25681,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="389" ht="15.75" customHeight="1" s="21">
       <c r="A389" t="inlineStr">
@@ -23806,6 +25746,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="390" ht="15.75" customHeight="1" s="21">
       <c r="A390" t="inlineStr">
@@ -23866,6 +25811,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="391" ht="15.75" customHeight="1" s="21">
       <c r="A391" t="inlineStr">
@@ -23930,6 +25880,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="392" ht="15.75" customHeight="1" s="21">
       <c r="A392" t="inlineStr">
@@ -23994,6 +25949,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="393" ht="15.75" customHeight="1" s="21">
       <c r="A393" t="inlineStr">
@@ -24058,6 +26018,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="394" ht="15.75" customHeight="1" s="21">
       <c r="A394" t="inlineStr">
@@ -24122,6 +26087,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="395" ht="15.75" customHeight="1" s="21">
       <c r="A395" t="inlineStr">
@@ -24186,6 +26156,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="396" ht="15.75" customHeight="1" s="21">
       <c r="A396" t="inlineStr">
@@ -24250,6 +26225,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="397" ht="15.75" customHeight="1" s="21">
       <c r="A397" t="inlineStr">
@@ -24314,6 +26294,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="398" ht="15.75" customHeight="1" s="21">
       <c r="A398" t="inlineStr">
@@ -24378,6 +26363,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="399" ht="15.75" customHeight="1" s="21">
       <c r="A399" t="inlineStr">
@@ -24442,6 +26432,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="400" ht="15.75" customHeight="1" s="21">
       <c r="A400" t="inlineStr">
@@ -24506,6 +26501,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="401" ht="15.75" customHeight="1" s="21">
       <c r="A401" t="inlineStr">
@@ -24570,6 +26570,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="402" ht="15.75" customHeight="1" s="21">
       <c r="A402" t="inlineStr">
@@ -24634,6 +26639,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="403" ht="15.75" customHeight="1" s="21">
       <c r="A403" t="inlineStr">
@@ -24698,6 +26708,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="404" ht="15.75" customHeight="1" s="21">
       <c r="A404" t="inlineStr">
@@ -24762,6 +26777,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="405" ht="15.75" customHeight="1" s="21">
       <c r="A405" t="inlineStr">
@@ -24826,6 +26846,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="406" ht="15.75" customHeight="1" s="21">
       <c r="A406" t="inlineStr">
@@ -24890,6 +26915,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="407" ht="15.75" customHeight="1" s="21">
       <c r="A407" t="inlineStr">
@@ -24954,6 +26984,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="408" ht="15.75" customHeight="1" s="21">
       <c r="A408" t="inlineStr">
@@ -25018,6 +27053,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="409" ht="15.75" customHeight="1" s="21">
       <c r="A409" t="inlineStr">
@@ -25082,6 +27122,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="410" ht="15.75" customHeight="1" s="21">
       <c r="A410" t="inlineStr">
@@ -25146,6 +27191,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="411" ht="15.75" customHeight="1" s="21">
       <c r="A411" t="inlineStr">
@@ -25210,6 +27260,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="412" ht="15.75" customHeight="1" s="21">
       <c r="A412" t="inlineStr">
@@ -25274,6 +27329,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="413" ht="15.75" customHeight="1" s="21">
       <c r="A413" t="inlineStr">
@@ -25338,6 +27398,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="414" ht="15.75" customHeight="1" s="21">
       <c r="A414" t="inlineStr">
@@ -25402,6 +27467,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="415" ht="15.75" customHeight="1" s="21">
       <c r="A415" t="inlineStr">
@@ -25466,6 +27536,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="416" ht="15.75" customHeight="1" s="21">
       <c r="A416" t="inlineStr">
@@ -25530,6 +27605,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="417" ht="15.75" customHeight="1" s="21">
       <c r="A417" t="inlineStr">
@@ -25594,6 +27674,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="418" ht="15.75" customHeight="1" s="21">
       <c r="A418" t="inlineStr">
@@ -25658,6 +27743,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="419" ht="15.75" customHeight="1" s="21">
       <c r="A419" t="inlineStr">
@@ -25722,6 +27812,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="420" ht="15.75" customHeight="1" s="21">
       <c r="A420" t="inlineStr">
@@ -25786,6 +27881,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="421" ht="15.75" customHeight="1" s="21">
       <c r="A421" t="inlineStr">
@@ -25850,6 +27950,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="422" ht="15.75" customHeight="1" s="21">
       <c r="A422" t="inlineStr">
@@ -25914,6 +28019,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="423" ht="15.75" customHeight="1" s="21">
       <c r="A423" t="inlineStr">
@@ -25978,6 +28088,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="424" ht="15.75" customHeight="1" s="21">
       <c r="A424" t="inlineStr">
@@ -26042,6 +28157,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="425" ht="15.75" customHeight="1" s="21">
       <c r="A425" t="inlineStr">
@@ -26106,6 +28226,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="426" ht="15.75" customHeight="1" s="21">
       <c r="A426" t="inlineStr">
@@ -26170,6 +28295,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="427" ht="15.75" customHeight="1" s="21">
       <c r="A427" t="inlineStr">
@@ -26234,6 +28364,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="428" ht="15.75" customHeight="1" s="21">
       <c r="A428" t="inlineStr">
@@ -26298,6 +28433,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="429" ht="15.75" customHeight="1" s="21">
       <c r="A429" t="inlineStr">
@@ -26362,6 +28502,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="430" ht="15.75" customHeight="1" s="21">
       <c r="A430" t="inlineStr">
@@ -26422,6 +28567,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="431" ht="15.75" customHeight="1" s="21">
       <c r="A431" t="inlineStr">
@@ -26486,6 +28636,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="432" ht="15.75" customHeight="1" s="21">
       <c r="A432" t="inlineStr">
@@ -26550,6 +28705,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="433" ht="15.75" customHeight="1" s="21">
       <c r="A433" t="inlineStr">
@@ -26614,6 +28774,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="434" ht="15.75" customHeight="1" s="21">
       <c r="A434" t="inlineStr">
@@ -26678,6 +28843,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="435" ht="15.75" customHeight="1" s="21">
       <c r="A435" t="inlineStr">
@@ -26742,6 +28912,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="436" ht="15.75" customHeight="1" s="21">
       <c r="A436" t="inlineStr">
@@ -26806,6 +28981,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="437" ht="15.75" customHeight="1" s="21">
       <c r="A437" t="inlineStr">
@@ -26870,6 +29050,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="438" ht="15.75" customHeight="1" s="21">
       <c r="A438" t="inlineStr">
@@ -26934,6 +29119,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="439" ht="15.75" customHeight="1" s="21">
       <c r="A439" t="inlineStr">
@@ -26998,6 +29188,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="440" ht="15.75" customHeight="1" s="21">
       <c r="A440" t="inlineStr">
@@ -27062,6 +29257,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="441" ht="15.75" customHeight="1" s="21">
       <c r="A441" t="inlineStr">
@@ -27126,6 +29326,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="442" ht="15.75" customHeight="1" s="21">
       <c r="A442" t="inlineStr">
@@ -27190,6 +29395,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="443" ht="15.75" customHeight="1" s="21">
       <c r="A443" t="inlineStr">
@@ -27254,6 +29464,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="444" ht="15.75" customHeight="1" s="21">
       <c r="A444" t="inlineStr">
@@ -27318,6 +29533,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="445" ht="15.75" customHeight="1" s="21">
       <c r="A445" t="inlineStr">
@@ -27382,6 +29602,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="446" ht="15.75" customHeight="1" s="21">
       <c r="A446" t="inlineStr">
@@ -27446,6 +29671,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="447" ht="15.75" customHeight="1" s="21">
       <c r="A447" t="inlineStr">
@@ -27510,6 +29740,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="448" ht="15.75" customHeight="1" s="21">
       <c r="A448" t="inlineStr">
@@ -27574,6 +29809,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="449" ht="15.75" customHeight="1" s="21">
       <c r="A449" t="inlineStr">
@@ -27638,6 +29878,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="450" ht="15.75" customHeight="1" s="21">
       <c r="A450" t="inlineStr">
@@ -27702,6 +29947,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="451" ht="15.75" customHeight="1" s="21">
       <c r="A451" t="inlineStr">
@@ -27766,6 +30016,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="452" ht="15.75" customHeight="1" s="21">
       <c r="A452" t="inlineStr">
@@ -27830,6 +30085,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="453" ht="15.75" customHeight="1" s="21">
       <c r="A453" t="inlineStr">
@@ -27894,6 +30154,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="454" ht="15.75" customHeight="1" s="21">
       <c r="A454" t="inlineStr">
@@ -27958,6 +30223,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="455" ht="15.75" customHeight="1" s="21">
       <c r="A455" t="inlineStr">
@@ -28022,6 +30292,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="456" ht="15.75" customHeight="1" s="21">
       <c r="A456" t="inlineStr">
@@ -28086,6 +30361,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="457" ht="15.75" customHeight="1" s="21">
       <c r="A457" t="inlineStr">
@@ -28150,6 +30430,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="458" ht="15.75" customHeight="1" s="21">
       <c r="A458" t="inlineStr">
@@ -28214,6 +30499,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="459" ht="15.75" customHeight="1" s="21">
       <c r="A459" t="inlineStr">
@@ -28278,6 +30568,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="460" ht="15.75" customHeight="1" s="21">
       <c r="A460" t="inlineStr">
@@ -28342,6 +30637,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="461" ht="15.75" customHeight="1" s="21">
       <c r="A461" t="inlineStr">
@@ -28406,6 +30706,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="462" ht="15.75" customHeight="1" s="21">
       <c r="A462" t="inlineStr">
@@ -28470,6 +30775,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="463" ht="15.75" customHeight="1" s="21">
       <c r="A463" t="inlineStr">
@@ -28534,6 +30844,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="464" ht="15.75" customHeight="1" s="21">
       <c r="A464" t="inlineStr">
@@ -28598,6 +30913,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="465" ht="15.75" customHeight="1" s="21">
       <c r="A465" t="inlineStr">
@@ -28662,6 +30982,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="466" ht="15.75" customHeight="1" s="21">
       <c r="A466" t="inlineStr">
@@ -28726,6 +31051,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="467" ht="15.75" customHeight="1" s="21">
       <c r="A467" t="inlineStr">
@@ -28790,6 +31120,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="468" ht="15.75" customHeight="1" s="21">
       <c r="A468" t="inlineStr">
@@ -28854,6 +31189,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="469" ht="15.75" customHeight="1" s="21">
       <c r="A469" t="inlineStr">
@@ -28918,6 +31258,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="470" ht="15.75" customHeight="1" s="21">
       <c r="A470" t="inlineStr">
@@ -28982,6 +31327,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="471" ht="15.75" customHeight="1" s="21">
       <c r="A471" t="inlineStr">
@@ -29046,6 +31396,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="472" ht="15.75" customHeight="1" s="21">
       <c r="A472" t="inlineStr">
@@ -29110,6 +31465,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="473" ht="15.75" customHeight="1" s="21">
       <c r="A473" t="inlineStr">
@@ -29174,6 +31534,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="474" ht="15.75" customHeight="1" s="21">
       <c r="A474" t="inlineStr">
@@ -29238,6 +31603,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="475" ht="15.75" customHeight="1" s="21">
       <c r="A475" t="inlineStr">
@@ -29302,6 +31672,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="476" ht="15.75" customHeight="1" s="21">
       <c r="A476" t="inlineStr">
@@ -29366,6 +31741,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="477" ht="15.75" customHeight="1" s="21">
       <c r="A477" t="inlineStr">
@@ -29430,6 +31810,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="478" ht="15.75" customHeight="1" s="21">
       <c r="A478" t="inlineStr">
@@ -29494,6 +31879,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="479" ht="15.75" customHeight="1" s="21">
       <c r="A479" t="inlineStr">
@@ -29558,6 +31948,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="480" ht="15.75" customHeight="1" s="21">
       <c r="A480" t="inlineStr">
@@ -29622,6 +32017,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="481" ht="15.75" customHeight="1" s="21">
       <c r="A481" t="inlineStr">
@@ -29686,6 +32086,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="482" ht="15.75" customHeight="1" s="21">
       <c r="A482" t="inlineStr">
@@ -29750,6 +32155,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="483" ht="15.75" customHeight="1" s="21">
       <c r="A483" t="inlineStr">
@@ -29814,6 +32224,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="484" ht="15.75" customHeight="1" s="21">
       <c r="A484" t="inlineStr">
@@ -29878,6 +32293,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="485" ht="15.75" customHeight="1" s="21">
       <c r="A485" t="inlineStr">
@@ -29942,6 +32362,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="486" ht="15.75" customHeight="1" s="21">
       <c r="A486" t="inlineStr">
@@ -30006,6 +32431,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="487" ht="15.75" customHeight="1" s="21">
       <c r="A487" t="inlineStr">
@@ -30070,6 +32500,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="488" ht="15.75" customHeight="1" s="21">
       <c r="A488" t="inlineStr">
@@ -30134,6 +32569,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="489" ht="15.75" customHeight="1" s="21">
       <c r="A489" t="inlineStr">
@@ -30198,6 +32638,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="490" ht="15.75" customHeight="1" s="21">
       <c r="A490" t="inlineStr">
@@ -30262,6 +32707,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="491" ht="15.75" customHeight="1" s="21">
       <c r="A491" t="inlineStr">
@@ -30326,6 +32776,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="492" ht="15.75" customHeight="1" s="21">
       <c r="A492" t="inlineStr">
@@ -30390,6 +32845,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="493" ht="15.75" customHeight="1" s="21">
       <c r="A493" t="inlineStr">
@@ -30454,6 +32914,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="494" ht="15.75" customHeight="1" s="21">
       <c r="A494" t="inlineStr">
@@ -30518,6 +32983,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="495" ht="15.75" customHeight="1" s="21">
       <c r="A495" t="inlineStr">
@@ -30582,6 +33052,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="496" ht="15.75" customHeight="1" s="21">
       <c r="A496" t="inlineStr">
@@ -30646,6 +33121,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="497" ht="15.75" customHeight="1" s="21">
       <c r="A497" t="inlineStr">
@@ -30710,6 +33190,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="498" ht="15.75" customHeight="1" s="21">
       <c r="A498" t="inlineStr">
@@ -30774,6 +33259,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="499" ht="15.75" customHeight="1" s="21">
       <c r="A499" t="inlineStr">
@@ -30838,6 +33328,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="500" ht="15.75" customHeight="1" s="21">
       <c r="A500" t="inlineStr">
@@ -30902,6 +33397,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="501" ht="15.75" customHeight="1" s="21">
       <c r="A501" t="inlineStr">
@@ -30966,6 +33466,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="502" ht="15.75" customHeight="1" s="21">
       <c r="A502" t="inlineStr">
@@ -31030,6 +33535,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="503" ht="15.75" customHeight="1" s="21">
       <c r="A503" t="inlineStr">
@@ -31094,6 +33604,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="504" ht="15.75" customHeight="1" s="21">
       <c r="A504" t="inlineStr">
@@ -31158,6 +33673,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="505" ht="15.75" customHeight="1" s="21">
       <c r="A505" t="inlineStr">
@@ -31222,6 +33742,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="506" ht="15.75" customHeight="1" s="21">
       <c r="A506" t="inlineStr">
@@ -31286,6 +33811,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="507" ht="15.75" customHeight="1" s="21">
       <c r="A507" t="inlineStr">
@@ -31350,6 +33880,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="508" ht="15.75" customHeight="1" s="21">
       <c r="A508" t="inlineStr">
@@ -31405,6 +33940,11 @@
           <t>УТОЧНИТЬ: вне import_заявки</t>
         </is>
       </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="509" ht="15.75" customHeight="1" s="21">
       <c r="A509" t="inlineStr">
@@ -31469,6 +34009,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="510" ht="15.75" customHeight="1" s="21">
       <c r="A510" t="inlineStr">
@@ -31533,6 +34078,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="511" ht="15.75" customHeight="1" s="21">
       <c r="A511" t="inlineStr">
@@ -31597,6 +34147,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="512" ht="15.75" customHeight="1" s="21">
       <c r="A512" t="inlineStr">
@@ -31661,6 +34216,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="513" ht="15.75" customHeight="1" s="21">
       <c r="A513" t="inlineStr">
@@ -31725,6 +34285,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="514" ht="15.75" customHeight="1" s="21">
       <c r="A514" t="inlineStr">
@@ -31789,6 +34354,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="515" ht="15.75" customHeight="1" s="21">
       <c r="A515" t="inlineStr">
@@ -31853,6 +34423,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="516" ht="15.75" customHeight="1" s="21">
       <c r="A516" t="inlineStr">
@@ -31917,6 +34492,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q516" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="517" ht="15.75" customHeight="1" s="21">
       <c r="A517" t="inlineStr">
@@ -31981,6 +34561,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="Q517" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="518" ht="15.75" customHeight="1" s="21">
       <c r="A518" t="inlineStr">
@@ -32045,6 +34630,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="Q518" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="519" ht="15.75" customHeight="1" s="21">
       <c r="A519" t="inlineStr">
@@ -32109,6 +34699,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="Q519" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="520" ht="15.75" customHeight="1" s="21">
       <c r="A520" t="inlineStr">
@@ -32173,6 +34768,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q520" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="521" ht="15.75" customHeight="1" s="21">
       <c r="A521" t="inlineStr">
@@ -32237,6 +34837,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="Q521" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="522" ht="15.75" customHeight="1" s="21">
       <c r="A522" t="inlineStr">
@@ -32301,6 +34906,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="Q522" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="523" ht="15.75" customHeight="1" s="21">
       <c r="A523" t="inlineStr">
@@ -32365,6 +34975,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="Q523" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="524" ht="15.75" customHeight="1" s="21">
       <c r="A524" t="inlineStr">
@@ -32427,6 +35042,11 @@
       <c r="P524" t="inlineStr">
         <is>
           <t>Абраамян Татьяна Викторовна</t>
+        </is>
+      </c>
+      <c r="Q524" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -32908,7 +35528,7 @@
     <row r="1000" ht="15.75" customHeight="1" s="21"/>
     <row r="1001" ht="15.75" customHeight="1" s="21"/>
   </sheetData>
-  <autoFilter ref="A1:P524"/>
+  <autoFilter ref="A1:Q524"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
